--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31120" windowHeight="13760"/>
+    <workbookView windowWidth="31120" windowHeight="13700"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>日期</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1693,163 +1696,323 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>477.510083312321</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>460.179972585153</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>452.272309581806</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>446.698428702462</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>435.203170943753</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>423.167495978268</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>416.665204093686</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>405.594452801676</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="4">
         <v>410.657806080651</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="4">
         <v>408.64571872195</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="4">
         <v>392.786665586946</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="4">
         <v>397.551514717864</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="4">
         <v>377.287011715518</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="4">
         <v>439.802507228529</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="4">
         <v>419.579326094659</v>
       </c>
-      <c r="R8" s="5">
+      <c r="R8" s="4">
         <v>427.253618776202</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="4">
         <v>473.537313440555</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="4">
         <v>504.83846731029</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="4">
         <v>538.040234576353</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V8" s="4">
         <v>584.680684992047</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="4">
         <v>558.410842207158</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8" s="4">
         <v>560.718673726151</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="Y8" s="4">
         <v>553.059204414606</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8" s="4">
         <v>532.850782162577</v>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>479.663105278797</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>450.226060237573</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>446.49602201333</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>441.516101643513</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>436.723535932768</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>426.273717778106</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>415.471833490793</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>405.395435743732</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
         <v>405.526210693069</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="4">
         <v>401.24318723317</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="4">
         <v>395.367585233927</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="4">
         <v>400.419861508885</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="4">
         <v>374.85397893975</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="4">
         <v>430.488614133024</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="4">
         <v>415.335700830734</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="4">
         <v>422.568728061064</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="4">
         <v>461.639028421042</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="4">
         <v>474.159354650376</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="4">
         <v>559.281670901527</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="4">
         <v>585.692266672926</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="4">
         <v>571.248928756925</v>
       </c>
-      <c r="X9" s="5">
+      <c r="X9" s="4">
         <v>570.213680505303</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="4">
         <v>564.381001825957</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="4">
         <v>541.969986591737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5">
+        <v>499.999953314644</v>
+      </c>
+      <c r="D10" s="5">
+        <v>453.072393128946</v>
+      </c>
+      <c r="E10" s="5">
+        <v>439.191376099889</v>
+      </c>
+      <c r="F10" s="5">
+        <v>432.016780667161</v>
+      </c>
+      <c r="G10" s="5">
+        <v>407.277749180335</v>
+      </c>
+      <c r="H10" s="5">
+        <v>416.156810739828</v>
+      </c>
+      <c r="I10" s="5">
+        <v>396.460923928478</v>
+      </c>
+      <c r="J10" s="5">
+        <v>385.469848189552</v>
+      </c>
+      <c r="K10" s="5">
+        <v>406.417160490052</v>
+      </c>
+      <c r="L10" s="5">
+        <v>410.327960088287</v>
+      </c>
+      <c r="M10" s="5">
+        <v>395.842158654537</v>
+      </c>
+      <c r="N10" s="5">
+        <v>404.988435928563</v>
+      </c>
+      <c r="O10" s="5">
+        <v>395.61937094767</v>
+      </c>
+      <c r="P10" s="5">
+        <v>449.579844359478</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>427.220788940556</v>
+      </c>
+      <c r="R10" s="5">
+        <v>449.693058150572</v>
+      </c>
+      <c r="S10" s="5">
+        <v>482.716871633252</v>
+      </c>
+      <c r="T10" s="5">
+        <v>503.372417895902</v>
+      </c>
+      <c r="U10" s="5">
+        <v>543.090929658904</v>
+      </c>
+      <c r="V10" s="5">
+        <v>584.52033161696</v>
+      </c>
+      <c r="W10" s="5">
+        <v>553.942760700385</v>
+      </c>
+      <c r="X10" s="5">
+        <v>566.9670145727</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>562.773969342367</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>504.491941381037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5">
+        <v>491.633524173506</v>
+      </c>
+      <c r="D11" s="5">
+        <v>453.101802437633</v>
+      </c>
+      <c r="E11" s="5">
+        <v>446.34160846947</v>
+      </c>
+      <c r="F11" s="5">
+        <v>439.628730505544</v>
+      </c>
+      <c r="G11" s="5">
+        <v>424.74350339526</v>
+      </c>
+      <c r="H11" s="5">
+        <v>421.494928893309</v>
+      </c>
+      <c r="I11" s="5">
+        <v>403.497951718332</v>
+      </c>
+      <c r="J11" s="5">
+        <v>394.583568771318</v>
+      </c>
+      <c r="K11" s="5">
+        <v>404.804859829541</v>
+      </c>
+      <c r="L11" s="5">
+        <v>409.195955870284</v>
+      </c>
+      <c r="M11" s="5">
+        <v>400.631554406933</v>
+      </c>
+      <c r="N11" s="5">
+        <v>407.249978603199</v>
+      </c>
+      <c r="O11" s="5">
+        <v>394.546730712444</v>
+      </c>
+      <c r="P11" s="5">
+        <v>441.223942478279</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>424.31534979812</v>
+      </c>
+      <c r="R11" s="5">
+        <v>439.642650357999</v>
+      </c>
+      <c r="S11" s="5">
+        <v>460.236281488575</v>
+      </c>
+      <c r="T11" s="5">
+        <v>472.289916725599</v>
+      </c>
+      <c r="U11" s="5">
+        <v>543.462612053415</v>
+      </c>
+      <c r="V11" s="5">
+        <v>560.216553982182</v>
+      </c>
+      <c r="W11" s="5">
+        <v>540.307229292708</v>
+      </c>
+      <c r="X11" s="5">
+        <v>538.756485421846</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>541.227909112238</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>514.952669537084</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31120" windowHeight="13700"/>
+    <workbookView windowHeight="13720"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>日期</t>
   </si>
@@ -126,6 +126,18 @@
   </si>
   <si>
     <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
   </si>
 </sst>
 </file>
@@ -139,7 +151,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +162,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -639,137 +644,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -777,7 +782,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1124,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1856,163 +1860,563 @@
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>499.999953314644</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>453.072393128946</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>439.191376099889</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>432.016780667161</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>407.277749180335</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>416.156810739828</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>396.460923928478</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>385.469848189552</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="4">
         <v>406.417160490052</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="4">
         <v>410.327960088287</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="4">
         <v>395.842158654537</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <v>404.988435928563</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="4">
         <v>395.61937094767</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="4">
         <v>449.579844359478</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>427.220788940556</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="4">
         <v>449.693058150572</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="4">
         <v>482.716871633252</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="4">
         <v>503.372417895902</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10" s="4">
         <v>543.090929658904</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10" s="4">
         <v>584.52033161696</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="4">
         <v>553.942760700385</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X10" s="4">
         <v>566.9670145727</v>
       </c>
-      <c r="Y10" s="5">
+      <c r="Y10" s="4">
         <v>562.773969342367</v>
       </c>
-      <c r="Z10" s="5">
+      <c r="Z10" s="4">
         <v>504.491941381037</v>
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>491.633524173506</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>453.101802437633</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>446.34160846947</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>439.628730505544</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>424.74350339526</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>421.494928893309</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
         <v>403.497951718332</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>394.583568771318</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="4">
         <v>404.804859829541</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="4">
         <v>409.195955870284</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="4">
         <v>400.631554406933</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="4">
         <v>407.249978603199</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="4">
         <v>394.546730712444</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P11" s="4">
         <v>441.223942478279</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q11" s="4">
         <v>424.31534979812</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R11" s="4">
         <v>439.642650357999</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="4">
         <v>460.236281488575</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="4">
         <v>472.289916725599</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11" s="4">
         <v>543.462612053415</v>
       </c>
-      <c r="V11" s="5">
+      <c r="V11" s="4">
         <v>560.216553982182</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="4">
         <v>540.307229292708</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="4">
         <v>538.756485421846</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="Y11" s="4">
         <v>541.227909112238</v>
       </c>
-      <c r="Z11" s="5">
+      <c r="Z11" s="4">
         <v>514.952669537084</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4">
+        <v>587.796164153375</v>
+      </c>
+      <c r="D12" s="4">
+        <v>504.316942851923</v>
+      </c>
+      <c r="E12" s="4">
+        <v>494.331973169521</v>
+      </c>
+      <c r="F12" s="4">
+        <v>491.328497909044</v>
+      </c>
+      <c r="G12" s="4">
+        <v>479.771178832867</v>
+      </c>
+      <c r="H12" s="4">
+        <v>453.208680454525</v>
+      </c>
+      <c r="I12" s="4">
+        <v>458.819491759793</v>
+      </c>
+      <c r="J12" s="4">
+        <v>440.684725061091</v>
+      </c>
+      <c r="K12" s="4">
+        <v>450.630291098853</v>
+      </c>
+      <c r="L12" s="4">
+        <v>449.545558758376</v>
+      </c>
+      <c r="M12" s="4">
+        <v>443.307753133256</v>
+      </c>
+      <c r="N12" s="4">
+        <v>450.702743528237</v>
+      </c>
+      <c r="O12" s="4">
+        <v>465.033343686606</v>
+      </c>
+      <c r="P12" s="4">
+        <v>508.499242476126</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>507.296391509249</v>
+      </c>
+      <c r="R12" s="4">
+        <v>521.156866018809</v>
+      </c>
+      <c r="S12" s="4">
+        <v>536.807765708613</v>
+      </c>
+      <c r="T12" s="4">
+        <v>548.526065028287</v>
+      </c>
+      <c r="U12" s="4">
+        <v>685.082886976314</v>
+      </c>
+      <c r="V12" s="4">
+        <v>763.334784525593</v>
+      </c>
+      <c r="W12" s="4">
+        <v>734.001244486975</v>
+      </c>
+      <c r="X12" s="4">
+        <v>779.902818039756</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>716.106993214605</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>616.578303975441</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4">
+        <v>587.796164153375</v>
+      </c>
+      <c r="D13" s="4">
+        <v>504.316942851923</v>
+      </c>
+      <c r="E13" s="4">
+        <v>494.331973169521</v>
+      </c>
+      <c r="F13" s="4">
+        <v>491.328497909044</v>
+      </c>
+      <c r="G13" s="4">
+        <v>479.771178832867</v>
+      </c>
+      <c r="H13" s="4">
+        <v>453.208680454525</v>
+      </c>
+      <c r="I13" s="4">
+        <v>458.819491759793</v>
+      </c>
+      <c r="J13" s="4">
+        <v>440.684725061091</v>
+      </c>
+      <c r="K13" s="4">
+        <v>450.630291098853</v>
+      </c>
+      <c r="L13" s="4">
+        <v>449.545558758376</v>
+      </c>
+      <c r="M13" s="4">
+        <v>443.307753133256</v>
+      </c>
+      <c r="N13" s="4">
+        <v>450.702743528237</v>
+      </c>
+      <c r="O13" s="4">
+        <v>457.440291665313</v>
+      </c>
+      <c r="P13" s="4">
+        <v>500.369109924276</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>499.777960298721</v>
+      </c>
+      <c r="R13" s="4">
+        <v>505.471132302952</v>
+      </c>
+      <c r="S13" s="4">
+        <v>507.356049415066</v>
+      </c>
+      <c r="T13" s="4">
+        <v>512.602125548294</v>
+      </c>
+      <c r="U13" s="4">
+        <v>670.17531627165</v>
+      </c>
+      <c r="V13" s="4">
+        <v>726.616402331308</v>
+      </c>
+      <c r="W13" s="4">
+        <v>704.501443943479</v>
+      </c>
+      <c r="X13" s="4">
+        <v>711.27837536407</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>699.133615647713</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>625.535906028361</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4">
+        <v>499.549823348457</v>
+      </c>
+      <c r="D14" s="4">
+        <v>488.346401846618</v>
+      </c>
+      <c r="E14" s="4">
+        <v>483.962575312921</v>
+      </c>
+      <c r="F14" s="4">
+        <v>449.806656353734</v>
+      </c>
+      <c r="G14" s="4">
+        <v>429.660390298135</v>
+      </c>
+      <c r="H14" s="4">
+        <v>405.640994968414</v>
+      </c>
+      <c r="I14" s="4">
+        <v>407.804620385826</v>
+      </c>
+      <c r="J14" s="4">
+        <v>368.978452340737</v>
+      </c>
+      <c r="K14" s="4">
+        <v>386.924895789642</v>
+      </c>
+      <c r="L14" s="4">
+        <v>384.361960921258</v>
+      </c>
+      <c r="M14" s="4">
+        <v>369.35244904694</v>
+      </c>
+      <c r="N14" s="4">
+        <v>374.485566433404</v>
+      </c>
+      <c r="O14" s="4">
+        <v>370.871255819542</v>
+      </c>
+      <c r="P14" s="4">
+        <v>442.360747950341</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>451.06694040604</v>
+      </c>
+      <c r="R14" s="4">
+        <v>463.727348223316</v>
+      </c>
+      <c r="S14" s="4">
+        <v>554.494460374124</v>
+      </c>
+      <c r="T14" s="4">
+        <v>533.405660109902</v>
+      </c>
+      <c r="U14" s="4">
+        <v>504.77001477848</v>
+      </c>
+      <c r="V14" s="4">
+        <v>598.285013548556</v>
+      </c>
+      <c r="W14" s="4">
+        <v>575.606838083591</v>
+      </c>
+      <c r="X14" s="4">
+        <v>561.767677780796</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>540.771977699468</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>454.819012387876</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:26">
+      <c r="A15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4">
+        <v>472.536298366511</v>
+      </c>
+      <c r="D15" s="4">
+        <v>442.293178701447</v>
+      </c>
+      <c r="E15" s="4">
+        <v>418.460641349833</v>
+      </c>
+      <c r="F15" s="4">
+        <v>379.729343526385</v>
+      </c>
+      <c r="G15" s="4">
+        <v>357.554449806281</v>
+      </c>
+      <c r="H15" s="4">
+        <v>351.164760507691</v>
+      </c>
+      <c r="I15" s="4">
+        <v>361.143339972786</v>
+      </c>
+      <c r="J15" s="4">
+        <v>364.937574958979</v>
+      </c>
+      <c r="K15" s="4">
+        <v>405.977722122311</v>
+      </c>
+      <c r="L15" s="4">
+        <v>452.11729011174</v>
+      </c>
+      <c r="M15" s="4">
+        <v>457.388888167619</v>
+      </c>
+      <c r="N15" s="4">
+        <v>480.602767594395</v>
+      </c>
+      <c r="O15" s="4">
+        <v>442.049464183192</v>
+      </c>
+      <c r="P15" s="4">
+        <v>516.080015152285</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>521.018410335694</v>
+      </c>
+      <c r="R15" s="4">
+        <v>556.661451904382</v>
+      </c>
+      <c r="S15" s="4">
+        <v>597.299244482497</v>
+      </c>
+      <c r="T15" s="4">
+        <v>570.747913284065</v>
+      </c>
+      <c r="U15" s="4">
+        <v>546.225376926151</v>
+      </c>
+      <c r="V15" s="4">
+        <v>596.900991390524</v>
+      </c>
+      <c r="W15" s="4">
+        <v>543.781405729068</v>
+      </c>
+      <c r="X15" s="4">
+        <v>526.970379771097</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>501.73994375129</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>441.077095838014</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:26">
+      <c r="A16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4">
+        <v>472.643909385578</v>
+      </c>
+      <c r="D16" s="4">
+        <v>453.594710014028</v>
+      </c>
+      <c r="E16" s="4">
+        <v>433.57755720157</v>
+      </c>
+      <c r="F16" s="4">
+        <v>391.305459734486</v>
+      </c>
+      <c r="G16" s="4">
+        <v>369.780193515868</v>
+      </c>
+      <c r="H16" s="4">
+        <v>368.88069597806</v>
+      </c>
+      <c r="I16" s="4">
+        <v>384.722219736534</v>
+      </c>
+      <c r="J16" s="4">
+        <v>366.790835033589</v>
+      </c>
+      <c r="K16" s="4">
+        <v>419.343623000763</v>
+      </c>
+      <c r="L16" s="4">
+        <v>461.353912245848</v>
+      </c>
+      <c r="M16" s="4">
+        <v>469.2880318489</v>
+      </c>
+      <c r="N16" s="4">
+        <v>474.025532960201</v>
+      </c>
+      <c r="O16" s="4">
+        <v>443.770464668559</v>
+      </c>
+      <c r="P16" s="4">
+        <v>524.999392889359</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>526.071441900764</v>
+      </c>
+      <c r="R16" s="4">
+        <v>548.972625456388</v>
+      </c>
+      <c r="S16" s="4">
+        <v>616.9049512091</v>
+      </c>
+      <c r="T16" s="4">
+        <v>592.135434022588</v>
+      </c>
+      <c r="U16" s="4">
+        <v>559.185423874112</v>
+      </c>
+      <c r="V16" s="4">
+        <v>598.11762282774</v>
+      </c>
+      <c r="W16" s="4">
+        <v>560.023574073716</v>
+      </c>
+      <c r="X16" s="4">
+        <v>531.883852636723</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>527.250120571998</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>454.183006631962</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>日期</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2419,6 +2422,86 @@
         <v>454.183006631962</v>
       </c>
     </row>
+    <row r="17" customFormat="1" spans="1:26">
+      <c r="A17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4">
+        <v>395.71</v>
+      </c>
+      <c r="D17" s="4">
+        <v>361.42</v>
+      </c>
+      <c r="E17" s="4">
+        <v>364.55</v>
+      </c>
+      <c r="F17" s="4">
+        <v>338.27</v>
+      </c>
+      <c r="G17" s="4">
+        <v>321.51</v>
+      </c>
+      <c r="H17" s="4">
+        <v>311.52</v>
+      </c>
+      <c r="I17" s="4">
+        <v>330.85</v>
+      </c>
+      <c r="J17" s="4">
+        <v>317.75</v>
+      </c>
+      <c r="K17" s="4">
+        <v>353.04</v>
+      </c>
+      <c r="L17" s="4">
+        <v>374.19</v>
+      </c>
+      <c r="M17" s="4">
+        <v>357.08</v>
+      </c>
+      <c r="N17" s="4">
+        <v>357.81</v>
+      </c>
+      <c r="O17" s="4">
+        <v>346.08</v>
+      </c>
+      <c r="P17" s="4">
+        <v>407.3</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>401.27</v>
+      </c>
+      <c r="R17" s="4">
+        <v>438.43</v>
+      </c>
+      <c r="S17" s="4">
+        <v>517.63</v>
+      </c>
+      <c r="T17" s="4">
+        <v>474.02</v>
+      </c>
+      <c r="U17" s="4">
+        <v>460.9</v>
+      </c>
+      <c r="V17" s="4">
+        <v>549.47</v>
+      </c>
+      <c r="W17" s="4">
+        <v>496.43</v>
+      </c>
+      <c r="X17" s="4">
+        <v>479.61</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>446.47</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>392.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>日期</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2502,6 +2505,166 @@
         <v>392.77</v>
       </c>
     </row>
+    <row r="18" customFormat="1" spans="1:26">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="4">
+        <v>376.442941884088</v>
+      </c>
+      <c r="D18" s="4">
+        <v>356.580208549079</v>
+      </c>
+      <c r="E18" s="4">
+        <v>342.059799722656</v>
+      </c>
+      <c r="F18" s="4">
+        <v>335.853365896346</v>
+      </c>
+      <c r="G18" s="4">
+        <v>320.15892150103</v>
+      </c>
+      <c r="H18" s="4">
+        <v>322.524663832116</v>
+      </c>
+      <c r="I18" s="4">
+        <v>327.401611501785</v>
+      </c>
+      <c r="J18" s="4">
+        <v>327.607721106834</v>
+      </c>
+      <c r="K18" s="4">
+        <v>356.039731776164</v>
+      </c>
+      <c r="L18" s="4">
+        <v>375.48745674762</v>
+      </c>
+      <c r="M18" s="4">
+        <v>342.249125428724</v>
+      </c>
+      <c r="N18" s="4">
+        <v>341.137787292126</v>
+      </c>
+      <c r="O18" s="4">
+        <v>332.258805843957</v>
+      </c>
+      <c r="P18" s="4">
+        <v>359.994386861925</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>372.467171072414</v>
+      </c>
+      <c r="R18" s="4">
+        <v>395.45076897851</v>
+      </c>
+      <c r="S18" s="4">
+        <v>465.496966000498</v>
+      </c>
+      <c r="T18" s="4">
+        <v>474.131850150183</v>
+      </c>
+      <c r="U18" s="4">
+        <v>456.500967612164</v>
+      </c>
+      <c r="V18" s="4">
+        <v>534.288006379043</v>
+      </c>
+      <c r="W18" s="4">
+        <v>488.405637210195</v>
+      </c>
+      <c r="X18" s="4">
+        <v>472.152961892626</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>414.008507774271</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>383.116509170904</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:26">
+      <c r="A19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="4">
+        <v>379.426735775396</v>
+      </c>
+      <c r="D19" s="4">
+        <v>359.962587086889</v>
+      </c>
+      <c r="E19" s="4">
+        <v>349.216665389313</v>
+      </c>
+      <c r="F19" s="4">
+        <v>335.853365896346</v>
+      </c>
+      <c r="G19" s="4">
+        <v>324.457858090029</v>
+      </c>
+      <c r="H19" s="4">
+        <v>323.490308404649</v>
+      </c>
+      <c r="I19" s="4">
+        <v>328.635484631891</v>
+      </c>
+      <c r="J19" s="4">
+        <v>327.607721106834</v>
+      </c>
+      <c r="K19" s="4">
+        <v>356.310481987627</v>
+      </c>
+      <c r="L19" s="4">
+        <v>376.11912128672</v>
+      </c>
+      <c r="M19" s="4">
+        <v>344.224007277478</v>
+      </c>
+      <c r="N19" s="4">
+        <v>341.835589362417</v>
+      </c>
+      <c r="O19" s="4">
+        <v>333.169357094433</v>
+      </c>
+      <c r="P19" s="4">
+        <v>359.994386861925</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>371.946735293125</v>
+      </c>
+      <c r="R19" s="4">
+        <v>395.45076897851</v>
+      </c>
+      <c r="S19" s="4">
+        <v>465.496966000498</v>
+      </c>
+      <c r="T19" s="4">
+        <v>474.131850150183</v>
+      </c>
+      <c r="U19" s="4">
+        <v>456.616582677012</v>
+      </c>
+      <c r="V19" s="4">
+        <v>534.288006379043</v>
+      </c>
+      <c r="W19" s="4">
+        <v>488.967119128676</v>
+      </c>
+      <c r="X19" s="4">
+        <v>477.219967509618</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>420.89477400533</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>384.206476720832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -2513,76 +2513,76 @@
         <v>27</v>
       </c>
       <c r="C18" s="4">
-        <v>376.442941884088</v>
+        <v>378.072939628393</v>
       </c>
       <c r="D18" s="4">
-        <v>356.580208549079</v>
+        <v>370.913220981877</v>
       </c>
       <c r="E18" s="4">
-        <v>342.059799722656</v>
+        <v>350.158879419133</v>
       </c>
       <c r="F18" s="4">
-        <v>335.853365896346</v>
+        <v>340.680076072717</v>
       </c>
       <c r="G18" s="4">
-        <v>320.15892150103</v>
+        <v>340.91254898401</v>
       </c>
       <c r="H18" s="4">
-        <v>322.524663832116</v>
+        <v>343.92367874255</v>
       </c>
       <c r="I18" s="4">
-        <v>327.401611501785</v>
+        <v>342.335464860256</v>
       </c>
       <c r="J18" s="4">
-        <v>327.607721106834</v>
+        <v>339.062566869322</v>
       </c>
       <c r="K18" s="4">
-        <v>356.039731776164</v>
+        <v>352.531349808055</v>
       </c>
       <c r="L18" s="4">
-        <v>375.48745674762</v>
+        <v>365.331175152831</v>
       </c>
       <c r="M18" s="4">
-        <v>342.249125428724</v>
+        <v>361.103908350326</v>
       </c>
       <c r="N18" s="4">
-        <v>341.137787292126</v>
+        <v>370.149765453412</v>
       </c>
       <c r="O18" s="4">
-        <v>332.258805843957</v>
+        <v>348.572609456131</v>
       </c>
       <c r="P18" s="4">
-        <v>359.994386861925</v>
+        <v>394.43004629552</v>
       </c>
       <c r="Q18" s="4">
-        <v>372.467171072414</v>
+        <v>392.904608392072</v>
       </c>
       <c r="R18" s="4">
-        <v>395.45076897851</v>
+        <v>437.125216039981</v>
       </c>
       <c r="S18" s="4">
-        <v>465.496966000498</v>
+        <v>492.069867546654</v>
       </c>
       <c r="T18" s="4">
-        <v>474.131850150183</v>
+        <v>485.015107075795</v>
       </c>
       <c r="U18" s="4">
-        <v>456.500967612164</v>
+        <v>502.887541582654</v>
       </c>
       <c r="V18" s="4">
-        <v>534.288006379043</v>
+        <v>607.123979504454</v>
       </c>
       <c r="W18" s="4">
-        <v>488.405637210195</v>
+        <v>545.491505446675</v>
       </c>
       <c r="X18" s="4">
-        <v>472.152961892626</v>
+        <v>510.106228226552</v>
       </c>
       <c r="Y18" s="4">
-        <v>414.008507774271</v>
+        <v>476.777628434456</v>
       </c>
       <c r="Z18" s="4">
-        <v>383.116509170904</v>
+        <v>432.639135899025</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:26">
@@ -2593,76 +2593,76 @@
         <v>28</v>
       </c>
       <c r="C19" s="4">
-        <v>379.426735775396</v>
+        <v>380.805758119525</v>
       </c>
       <c r="D19" s="4">
-        <v>359.962587086889</v>
+        <v>373.578846780217</v>
       </c>
       <c r="E19" s="4">
-        <v>349.216665389313</v>
+        <v>357.297633901751</v>
       </c>
       <c r="F19" s="4">
-        <v>335.853365896346</v>
+        <v>347.48308376995</v>
       </c>
       <c r="G19" s="4">
-        <v>324.457858090029</v>
+        <v>346.867324417275</v>
       </c>
       <c r="H19" s="4">
-        <v>323.490308404649</v>
+        <v>345.801602123749</v>
       </c>
       <c r="I19" s="4">
-        <v>328.635484631891</v>
+        <v>347.214156454185</v>
       </c>
       <c r="J19" s="4">
-        <v>327.607721106834</v>
+        <v>342.551811788602</v>
       </c>
       <c r="K19" s="4">
-        <v>356.310481987627</v>
+        <v>355.122312012989</v>
       </c>
       <c r="L19" s="4">
-        <v>376.11912128672</v>
+        <v>367.776109788426</v>
       </c>
       <c r="M19" s="4">
-        <v>344.224007277478</v>
+        <v>367.099675246369</v>
       </c>
       <c r="N19" s="4">
-        <v>341.835589362417</v>
+        <v>373.210642054964</v>
       </c>
       <c r="O19" s="4">
-        <v>333.169357094433</v>
+        <v>353.025070654336</v>
       </c>
       <c r="P19" s="4">
-        <v>359.994386861925</v>
+        <v>394.43004629552</v>
       </c>
       <c r="Q19" s="4">
-        <v>371.946735293125</v>
+        <v>394.341838133525</v>
       </c>
       <c r="R19" s="4">
-        <v>395.45076897851</v>
+        <v>437.125216039981</v>
       </c>
       <c r="S19" s="4">
-        <v>465.496966000498</v>
+        <v>492.069867546654</v>
       </c>
       <c r="T19" s="4">
-        <v>474.131850150183</v>
+        <v>488.97576206992</v>
       </c>
       <c r="U19" s="4">
-        <v>456.616582677012</v>
+        <v>506.477831957841</v>
       </c>
       <c r="V19" s="4">
-        <v>534.288006379043</v>
+        <v>609.689416465988</v>
       </c>
       <c r="W19" s="4">
-        <v>488.967119128676</v>
+        <v>547.597940856486</v>
       </c>
       <c r="X19" s="4">
-        <v>477.219967509618</v>
+        <v>516.253494592302</v>
       </c>
       <c r="Y19" s="4">
-        <v>420.89477400533</v>
+        <v>481.684634660761</v>
       </c>
       <c r="Z19" s="4">
-        <v>384.206476720832</v>
+        <v>434.858421074339</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>日期</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2665,6 +2668,86 @@
         <v>434.858421074339</v>
       </c>
     </row>
+    <row r="20" customFormat="1" spans="1:26">
+      <c r="A20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4">
+        <v>388.202730542476</v>
+      </c>
+      <c r="D20" s="4">
+        <v>392.737073553957</v>
+      </c>
+      <c r="E20" s="4">
+        <v>377.404615127363</v>
+      </c>
+      <c r="F20" s="4">
+        <v>379.972109581057</v>
+      </c>
+      <c r="G20" s="4">
+        <v>365.620315887356</v>
+      </c>
+      <c r="H20" s="4">
+        <v>370.931177453823</v>
+      </c>
+      <c r="I20" s="4">
+        <v>367.365636149892</v>
+      </c>
+      <c r="J20" s="4">
+        <v>353.951475591681</v>
+      </c>
+      <c r="K20" s="4">
+        <v>392.55742788183</v>
+      </c>
+      <c r="L20" s="4">
+        <v>407.945537486317</v>
+      </c>
+      <c r="M20" s="4">
+        <v>387.496009377131</v>
+      </c>
+      <c r="N20" s="4">
+        <v>393.647372856362</v>
+      </c>
+      <c r="O20" s="4">
+        <v>376.884285401997</v>
+      </c>
+      <c r="P20" s="4">
+        <v>392.912747716845</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>401.737445267995</v>
+      </c>
+      <c r="R20" s="4">
+        <v>415.806789729676</v>
+      </c>
+      <c r="S20" s="4">
+        <v>480.694310831758</v>
+      </c>
+      <c r="T20" s="4">
+        <v>485.011688657326</v>
+      </c>
+      <c r="U20" s="4">
+        <v>510.579394473448</v>
+      </c>
+      <c r="V20" s="4">
+        <v>608.314859185175</v>
+      </c>
+      <c r="W20" s="4">
+        <v>545.225274308285</v>
+      </c>
+      <c r="X20" s="4">
+        <v>520.384944056136</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>470.222375215246</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>429.712100589911</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>日期</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2748,6 +2751,166 @@
         <v>429.712100589911</v>
       </c>
     </row>
+    <row r="21" customFormat="1" spans="1:26">
+      <c r="A21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="4">
+        <v>448.85</v>
+      </c>
+      <c r="D21" s="4">
+        <v>432.14</v>
+      </c>
+      <c r="E21" s="4">
+        <v>407.11</v>
+      </c>
+      <c r="F21" s="4">
+        <v>392.68</v>
+      </c>
+      <c r="G21" s="4">
+        <v>375.48</v>
+      </c>
+      <c r="H21" s="4">
+        <v>375.84</v>
+      </c>
+      <c r="I21" s="4">
+        <v>375.23</v>
+      </c>
+      <c r="J21" s="4">
+        <v>352.01</v>
+      </c>
+      <c r="K21" s="4">
+        <v>379.48</v>
+      </c>
+      <c r="L21" s="4">
+        <v>416.92</v>
+      </c>
+      <c r="M21" s="4">
+        <v>395.9</v>
+      </c>
+      <c r="N21" s="4">
+        <v>408.56</v>
+      </c>
+      <c r="O21" s="4">
+        <v>391.77</v>
+      </c>
+      <c r="P21" s="4">
+        <v>430.21</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>424.86</v>
+      </c>
+      <c r="R21" s="4">
+        <v>441.59</v>
+      </c>
+      <c r="S21" s="4">
+        <v>492.17</v>
+      </c>
+      <c r="T21" s="4">
+        <v>496.32</v>
+      </c>
+      <c r="U21" s="4">
+        <v>459.16</v>
+      </c>
+      <c r="V21" s="4">
+        <v>538.34</v>
+      </c>
+      <c r="W21" s="4">
+        <v>507.39</v>
+      </c>
+      <c r="X21" s="4">
+        <v>497.35</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>468.25</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>415.64</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:26">
+      <c r="A22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="4">
+        <v>448.79</v>
+      </c>
+      <c r="D22" s="4">
+        <v>432.14</v>
+      </c>
+      <c r="E22" s="4">
+        <v>410.77</v>
+      </c>
+      <c r="F22" s="4">
+        <v>395.01</v>
+      </c>
+      <c r="G22" s="4">
+        <v>376.18</v>
+      </c>
+      <c r="H22" s="4">
+        <v>376.16</v>
+      </c>
+      <c r="I22" s="4">
+        <v>375.45</v>
+      </c>
+      <c r="J22" s="4">
+        <v>351.61</v>
+      </c>
+      <c r="K22" s="4">
+        <v>379.48</v>
+      </c>
+      <c r="L22" s="4">
+        <v>416.92</v>
+      </c>
+      <c r="M22" s="4">
+        <v>395.9</v>
+      </c>
+      <c r="N22" s="4">
+        <v>408.56</v>
+      </c>
+      <c r="O22" s="4">
+        <v>391.77</v>
+      </c>
+      <c r="P22" s="4">
+        <v>428.54</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>424.11</v>
+      </c>
+      <c r="R22" s="4">
+        <v>441.59</v>
+      </c>
+      <c r="S22" s="4">
+        <v>492.17</v>
+      </c>
+      <c r="T22" s="4">
+        <v>496.32</v>
+      </c>
+      <c r="U22" s="4">
+        <v>459.44</v>
+      </c>
+      <c r="V22" s="4">
+        <v>538.34</v>
+      </c>
+      <c r="W22" s="4">
+        <v>507.39</v>
+      </c>
+      <c r="X22" s="4">
+        <v>499.4</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>473.86</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>416.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t>日期</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2911,6 +2914,166 @@
         <v>416.23</v>
       </c>
     </row>
+    <row r="23" customFormat="1" spans="1:26">
+      <c r="A23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4">
+        <v>441.58</v>
+      </c>
+      <c r="D23" s="4">
+        <v>416.82</v>
+      </c>
+      <c r="E23" s="4">
+        <v>400.59</v>
+      </c>
+      <c r="F23" s="4">
+        <v>382.56</v>
+      </c>
+      <c r="G23" s="4">
+        <v>369.17</v>
+      </c>
+      <c r="H23" s="4">
+        <v>370.27</v>
+      </c>
+      <c r="I23" s="4">
+        <v>359.27</v>
+      </c>
+      <c r="J23" s="4">
+        <v>345.84</v>
+      </c>
+      <c r="K23" s="4">
+        <v>350.84</v>
+      </c>
+      <c r="L23" s="4">
+        <v>380.34</v>
+      </c>
+      <c r="M23" s="4">
+        <v>384.74</v>
+      </c>
+      <c r="N23" s="4">
+        <v>388.74</v>
+      </c>
+      <c r="O23" s="4">
+        <v>375.28</v>
+      </c>
+      <c r="P23" s="4">
+        <v>412.23</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>390.47</v>
+      </c>
+      <c r="R23" s="4">
+        <v>394.2</v>
+      </c>
+      <c r="S23" s="4">
+        <v>418.68</v>
+      </c>
+      <c r="T23" s="4">
+        <v>441.73</v>
+      </c>
+      <c r="U23" s="4">
+        <v>412.57</v>
+      </c>
+      <c r="V23" s="4">
+        <v>477.14</v>
+      </c>
+      <c r="W23" s="4">
+        <v>457.3</v>
+      </c>
+      <c r="X23" s="4">
+        <v>451.62</v>
+      </c>
+      <c r="Y23" s="4">
+        <v>423.55</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>377.56</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:26">
+      <c r="A24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="4">
+        <v>441.81</v>
+      </c>
+      <c r="D24" s="4">
+        <v>416.82</v>
+      </c>
+      <c r="E24" s="4">
+        <v>403.27</v>
+      </c>
+      <c r="F24" s="4">
+        <v>383.89</v>
+      </c>
+      <c r="G24" s="4">
+        <v>369.21</v>
+      </c>
+      <c r="H24" s="4">
+        <v>370.46</v>
+      </c>
+      <c r="I24" s="4">
+        <v>359.29</v>
+      </c>
+      <c r="J24" s="4">
+        <v>345.34</v>
+      </c>
+      <c r="K24" s="4">
+        <v>350.84</v>
+      </c>
+      <c r="L24" s="4">
+        <v>380.34</v>
+      </c>
+      <c r="M24" s="4">
+        <v>384.74</v>
+      </c>
+      <c r="N24" s="4">
+        <v>388.74</v>
+      </c>
+      <c r="O24" s="4">
+        <v>375.28</v>
+      </c>
+      <c r="P24" s="4">
+        <v>411.63</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>389.55</v>
+      </c>
+      <c r="R24" s="4">
+        <v>394.2</v>
+      </c>
+      <c r="S24" s="4">
+        <v>418.68</v>
+      </c>
+      <c r="T24" s="4">
+        <v>441.73</v>
+      </c>
+      <c r="U24" s="4">
+        <v>412.71</v>
+      </c>
+      <c r="V24" s="4">
+        <v>477.14</v>
+      </c>
+      <c r="W24" s="4">
+        <v>457.3</v>
+      </c>
+      <c r="X24" s="4">
+        <v>455.33</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>428.95</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>377.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="13720"/>
+    <workbookView windowHeight="11000"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>日期</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3074,6 +3080,246 @@
         <v>377.92</v>
       </c>
     </row>
+    <row r="25" customFormat="1" spans="1:26">
+      <c r="A25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4">
+        <v>393.82</v>
+      </c>
+      <c r="D25" s="4">
+        <v>382.09</v>
+      </c>
+      <c r="E25" s="4">
+        <v>373.63</v>
+      </c>
+      <c r="F25" s="4">
+        <v>371.44</v>
+      </c>
+      <c r="G25" s="4">
+        <v>353.25</v>
+      </c>
+      <c r="H25" s="4">
+        <v>355.8</v>
+      </c>
+      <c r="I25" s="4">
+        <v>367.67</v>
+      </c>
+      <c r="J25" s="4">
+        <v>370.23</v>
+      </c>
+      <c r="K25" s="4">
+        <v>425.26</v>
+      </c>
+      <c r="L25" s="4">
+        <v>474.38</v>
+      </c>
+      <c r="M25" s="4">
+        <v>458.86</v>
+      </c>
+      <c r="N25" s="4">
+        <v>478.82</v>
+      </c>
+      <c r="O25" s="4">
+        <v>449.94</v>
+      </c>
+      <c r="P25" s="4">
+        <v>500.78</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>486.63</v>
+      </c>
+      <c r="R25" s="4">
+        <v>500.37</v>
+      </c>
+      <c r="S25" s="4">
+        <v>549.2</v>
+      </c>
+      <c r="T25" s="4">
+        <v>540.96</v>
+      </c>
+      <c r="U25" s="4">
+        <v>492.61</v>
+      </c>
+      <c r="V25" s="4">
+        <v>587.13</v>
+      </c>
+      <c r="W25" s="4">
+        <v>530.93</v>
+      </c>
+      <c r="X25" s="4">
+        <v>484.88</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>450.5</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>386.19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:26">
+      <c r="A26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="4">
+        <v>393.94</v>
+      </c>
+      <c r="D26" s="4">
+        <v>382.09</v>
+      </c>
+      <c r="E26" s="4">
+        <v>376.9</v>
+      </c>
+      <c r="F26" s="4">
+        <v>373.55</v>
+      </c>
+      <c r="G26" s="4">
+        <v>353.75</v>
+      </c>
+      <c r="H26" s="4">
+        <v>356.07</v>
+      </c>
+      <c r="I26" s="4">
+        <v>367.78</v>
+      </c>
+      <c r="J26" s="4">
+        <v>369.71</v>
+      </c>
+      <c r="K26" s="4">
+        <v>425.26</v>
+      </c>
+      <c r="L26" s="4">
+        <v>474.38</v>
+      </c>
+      <c r="M26" s="4">
+        <v>458.86</v>
+      </c>
+      <c r="N26" s="4">
+        <v>478.82</v>
+      </c>
+      <c r="O26" s="4">
+        <v>449.94</v>
+      </c>
+      <c r="P26" s="4">
+        <v>499.45</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>485.73</v>
+      </c>
+      <c r="R26" s="4">
+        <v>500.37</v>
+      </c>
+      <c r="S26" s="4">
+        <v>549.2</v>
+      </c>
+      <c r="T26" s="4">
+        <v>540.96</v>
+      </c>
+      <c r="U26" s="4">
+        <v>492.58</v>
+      </c>
+      <c r="V26" s="4">
+        <v>587.13</v>
+      </c>
+      <c r="W26" s="4">
+        <v>530.93</v>
+      </c>
+      <c r="X26" s="4">
+        <v>488.24</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>456.11</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>386.67</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:26">
+      <c r="A27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="4">
+        <v>433.25</v>
+      </c>
+      <c r="D27" s="4">
+        <v>419.74</v>
+      </c>
+      <c r="E27" s="4">
+        <v>396.44</v>
+      </c>
+      <c r="F27" s="4">
+        <v>391.43</v>
+      </c>
+      <c r="G27" s="4">
+        <v>362.52</v>
+      </c>
+      <c r="H27" s="4">
+        <v>369.54</v>
+      </c>
+      <c r="I27" s="4">
+        <v>373.27</v>
+      </c>
+      <c r="J27" s="4">
+        <v>371.32</v>
+      </c>
+      <c r="K27" s="4">
+        <v>439.79</v>
+      </c>
+      <c r="L27" s="4">
+        <v>489.58</v>
+      </c>
+      <c r="M27" s="4">
+        <v>478.5</v>
+      </c>
+      <c r="N27" s="4">
+        <v>476.74</v>
+      </c>
+      <c r="O27" s="4">
+        <v>448.32</v>
+      </c>
+      <c r="P27" s="4">
+        <v>498.11</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>475.62</v>
+      </c>
+      <c r="R27" s="4">
+        <v>500.24</v>
+      </c>
+      <c r="S27" s="4">
+        <v>566.01</v>
+      </c>
+      <c r="T27" s="4">
+        <v>566.02</v>
+      </c>
+      <c r="U27" s="4">
+        <v>519.67</v>
+      </c>
+      <c r="V27" s="4">
+        <v>622.73</v>
+      </c>
+      <c r="W27" s="4">
+        <v>566.61</v>
+      </c>
+      <c r="X27" s="4">
+        <v>528.61</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>472.16</v>
+      </c>
+      <c r="Z27" s="4">
+        <v>410.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="11000"/>
+    <workbookView windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
     <t>日期</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3320,6 +3326,166 @@
         <v>410.04</v>
       </c>
     </row>
+    <row r="28" customFormat="1" spans="1:26">
+      <c r="A28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="4">
+        <v>396.34</v>
+      </c>
+      <c r="D28" s="4">
+        <v>381.1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>372.69</v>
+      </c>
+      <c r="F28" s="4">
+        <v>367.09</v>
+      </c>
+      <c r="G28" s="4">
+        <v>359.03</v>
+      </c>
+      <c r="H28" s="4">
+        <v>356.59</v>
+      </c>
+      <c r="I28" s="4">
+        <v>365.66</v>
+      </c>
+      <c r="J28" s="4">
+        <v>365.99</v>
+      </c>
+      <c r="K28" s="4">
+        <v>405.73</v>
+      </c>
+      <c r="L28" s="4">
+        <v>439.57</v>
+      </c>
+      <c r="M28" s="4">
+        <v>418.75</v>
+      </c>
+      <c r="N28" s="4">
+        <v>430.5</v>
+      </c>
+      <c r="O28" s="4">
+        <v>404.26</v>
+      </c>
+      <c r="P28" s="4">
+        <v>456.27</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>429.36</v>
+      </c>
+      <c r="R28" s="4">
+        <v>470.38</v>
+      </c>
+      <c r="S28" s="4">
+        <v>505.13</v>
+      </c>
+      <c r="T28" s="4">
+        <v>512.47</v>
+      </c>
+      <c r="U28" s="4">
+        <v>466.19</v>
+      </c>
+      <c r="V28" s="4">
+        <v>562.67</v>
+      </c>
+      <c r="W28" s="4">
+        <v>490.05</v>
+      </c>
+      <c r="X28" s="4">
+        <v>465.2</v>
+      </c>
+      <c r="Y28" s="4">
+        <v>411.23</v>
+      </c>
+      <c r="Z28" s="4">
+        <v>364.92</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:26">
+      <c r="A29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4">
+        <v>382.35</v>
+      </c>
+      <c r="D29" s="4">
+        <v>364.28</v>
+      </c>
+      <c r="E29" s="4">
+        <v>342.7</v>
+      </c>
+      <c r="F29" s="4">
+        <v>327.87</v>
+      </c>
+      <c r="G29" s="4">
+        <v>314.14</v>
+      </c>
+      <c r="H29" s="4">
+        <v>324.67</v>
+      </c>
+      <c r="I29" s="4">
+        <v>327.57</v>
+      </c>
+      <c r="J29" s="4">
+        <v>323.49</v>
+      </c>
+      <c r="K29" s="4">
+        <v>371.59</v>
+      </c>
+      <c r="L29" s="4">
+        <v>421.31</v>
+      </c>
+      <c r="M29" s="4">
+        <v>407.96</v>
+      </c>
+      <c r="N29" s="4">
+        <v>407.96</v>
+      </c>
+      <c r="O29" s="4">
+        <v>397.4</v>
+      </c>
+      <c r="P29" s="4">
+        <v>426.82</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>390.89</v>
+      </c>
+      <c r="R29" s="4">
+        <v>396.16</v>
+      </c>
+      <c r="S29" s="4">
+        <v>413.86</v>
+      </c>
+      <c r="T29" s="4">
+        <v>414.41</v>
+      </c>
+      <c r="U29" s="4">
+        <v>379.5</v>
+      </c>
+      <c r="V29" s="4">
+        <v>439.34</v>
+      </c>
+      <c r="W29" s="4">
+        <v>406.75</v>
+      </c>
+      <c r="X29" s="4">
+        <v>389.85</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>378.13</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>333.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>日期</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1886,7 +1889,7 @@
         <v>541.969986591737</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" customFormat="1" spans="1:26">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -1894,1596 +1897,1196 @@
         <v>27</v>
       </c>
       <c r="C10" s="4">
-        <v>499.999953314644</v>
+        <v>491.21</v>
       </c>
       <c r="D10" s="4">
-        <v>453.072393128946</v>
+        <v>446.82</v>
       </c>
       <c r="E10" s="4">
-        <v>439.191376099889</v>
+        <v>427.72</v>
       </c>
       <c r="F10" s="4">
-        <v>432.016780667161</v>
+        <v>399.2</v>
       </c>
       <c r="G10" s="4">
-        <v>407.277749180335</v>
+        <v>381.13</v>
       </c>
       <c r="H10" s="4">
-        <v>416.156810739828</v>
+        <v>360.89</v>
       </c>
       <c r="I10" s="4">
-        <v>396.460923928478</v>
+        <v>354.41</v>
       </c>
       <c r="J10" s="4">
-        <v>385.469848189552</v>
+        <v>348.38</v>
       </c>
       <c r="K10" s="4">
-        <v>406.417160490052</v>
+        <v>398.52</v>
       </c>
       <c r="L10" s="4">
-        <v>410.327960088287</v>
+        <v>419.4</v>
       </c>
       <c r="M10" s="4">
-        <v>395.842158654537</v>
+        <v>416.39</v>
       </c>
       <c r="N10" s="4">
-        <v>404.988435928563</v>
+        <v>434.9</v>
       </c>
       <c r="O10" s="4">
-        <v>395.61937094767</v>
+        <v>398.66</v>
       </c>
       <c r="P10" s="4">
-        <v>449.579844359478</v>
+        <v>470.25</v>
       </c>
       <c r="Q10" s="4">
-        <v>427.220788940556</v>
+        <v>483.76</v>
       </c>
       <c r="R10" s="4">
-        <v>449.693058150572</v>
+        <v>515.12</v>
       </c>
       <c r="S10" s="4">
-        <v>482.716871633252</v>
+        <v>577.94</v>
       </c>
       <c r="T10" s="4">
-        <v>503.372417895902</v>
+        <v>589.94</v>
       </c>
       <c r="U10" s="4">
-        <v>543.090929658904</v>
+        <v>568.03</v>
       </c>
       <c r="V10" s="4">
-        <v>584.52033161696</v>
+        <v>619.35</v>
       </c>
       <c r="W10" s="4">
-        <v>553.942760700385</v>
+        <v>619.56</v>
       </c>
       <c r="X10" s="4">
-        <v>566.9670145727</v>
+        <v>606.77</v>
       </c>
       <c r="Y10" s="4">
-        <v>562.773969342367</v>
+        <v>579.41</v>
       </c>
       <c r="Z10" s="4">
-        <v>504.491941381037</v>
+        <v>460.15</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" customFormat="1" spans="1:26">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4">
-        <v>491.633524173506</v>
+        <v>486.98</v>
       </c>
       <c r="D11" s="4">
-        <v>453.101802437633</v>
+        <v>466.53</v>
       </c>
       <c r="E11" s="4">
-        <v>446.34160846947</v>
+        <v>460.93</v>
       </c>
       <c r="F11" s="4">
-        <v>439.628730505544</v>
+        <v>431.58</v>
       </c>
       <c r="G11" s="4">
-        <v>424.74350339526</v>
+        <v>407.48</v>
       </c>
       <c r="H11" s="4">
-        <v>421.494928893309</v>
+        <v>394.1</v>
       </c>
       <c r="I11" s="4">
-        <v>403.497951718332</v>
+        <v>398.41</v>
       </c>
       <c r="J11" s="4">
-        <v>394.583568771318</v>
+        <v>370.58</v>
       </c>
       <c r="K11" s="4">
-        <v>404.804859829541</v>
+        <v>402.66</v>
       </c>
       <c r="L11" s="4">
-        <v>409.195955870284</v>
+        <v>411.64</v>
       </c>
       <c r="M11" s="4">
-        <v>400.631554406933</v>
+        <v>409.81</v>
       </c>
       <c r="N11" s="4">
-        <v>407.249978603199</v>
+        <v>434.38</v>
       </c>
       <c r="O11" s="4">
-        <v>394.546730712444</v>
+        <v>398.72</v>
       </c>
       <c r="P11" s="4">
-        <v>441.223942478279</v>
+        <v>495.88</v>
       </c>
       <c r="Q11" s="4">
-        <v>424.31534979812</v>
+        <v>516.21</v>
       </c>
       <c r="R11" s="4">
-        <v>439.642650357999</v>
+        <v>566.66</v>
       </c>
       <c r="S11" s="4">
-        <v>460.236281488575</v>
+        <v>601.06</v>
       </c>
       <c r="T11" s="4">
-        <v>472.289916725599</v>
+        <v>584.16</v>
       </c>
       <c r="U11" s="4">
-        <v>543.462612053415</v>
+        <v>576.81</v>
       </c>
       <c r="V11" s="4">
-        <v>560.216553982182</v>
+        <v>601.24</v>
       </c>
       <c r="W11" s="4">
-        <v>540.307229292708</v>
+        <v>591.78</v>
       </c>
       <c r="X11" s="4">
-        <v>538.756485421846</v>
+        <v>578.29</v>
       </c>
       <c r="Y11" s="4">
-        <v>541.227909112238</v>
+        <v>545.63</v>
       </c>
       <c r="Z11" s="4">
-        <v>514.952669537084</v>
+        <v>453.35</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" customFormat="1" spans="1:26">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="4">
-        <v>587.796164153375</v>
+        <v>499.55</v>
       </c>
       <c r="D12" s="4">
-        <v>504.316942851923</v>
+        <v>488.35</v>
       </c>
       <c r="E12" s="4">
-        <v>494.331973169521</v>
+        <v>483.96</v>
       </c>
       <c r="F12" s="4">
-        <v>491.328497909044</v>
+        <v>449.81</v>
       </c>
       <c r="G12" s="4">
-        <v>479.771178832867</v>
+        <v>429.66</v>
       </c>
       <c r="H12" s="4">
-        <v>453.208680454525</v>
+        <v>405.64</v>
       </c>
       <c r="I12" s="4">
-        <v>458.819491759793</v>
+        <v>407.8</v>
       </c>
       <c r="J12" s="4">
-        <v>440.684725061091</v>
+        <v>368.98</v>
       </c>
       <c r="K12" s="4">
-        <v>450.630291098853</v>
+        <v>386.92</v>
       </c>
       <c r="L12" s="4">
-        <v>449.545558758376</v>
+        <v>384.36</v>
       </c>
       <c r="M12" s="4">
-        <v>443.307753133256</v>
+        <v>369.35</v>
       </c>
       <c r="N12" s="4">
-        <v>450.702743528237</v>
+        <v>374.49</v>
       </c>
       <c r="O12" s="4">
-        <v>465.033343686606</v>
+        <v>370.87</v>
       </c>
       <c r="P12" s="4">
-        <v>508.499242476126</v>
+        <v>442.36</v>
       </c>
       <c r="Q12" s="4">
-        <v>507.296391509249</v>
+        <v>451.07</v>
       </c>
       <c r="R12" s="4">
-        <v>521.156866018809</v>
+        <v>463.73</v>
       </c>
       <c r="S12" s="4">
-        <v>536.807765708613</v>
+        <v>554.49</v>
       </c>
       <c r="T12" s="4">
-        <v>548.526065028287</v>
+        <v>533.41</v>
       </c>
       <c r="U12" s="4">
-        <v>685.082886976314</v>
+        <v>504.77</v>
       </c>
       <c r="V12" s="4">
-        <v>763.334784525593</v>
+        <v>598.29</v>
       </c>
       <c r="W12" s="4">
-        <v>734.001244486975</v>
+        <v>575.61</v>
       </c>
       <c r="X12" s="4">
-        <v>779.902818039756</v>
+        <v>561.77</v>
       </c>
       <c r="Y12" s="4">
-        <v>716.106993214605</v>
+        <v>540.77</v>
       </c>
       <c r="Z12" s="4">
-        <v>616.578303975441</v>
+        <v>454.82</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" customFormat="1" spans="1:26">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4">
-        <v>587.796164153375</v>
+        <v>466.36</v>
       </c>
       <c r="D13" s="4">
-        <v>504.316942851923</v>
+        <v>433.26</v>
       </c>
       <c r="E13" s="4">
-        <v>494.331973169521</v>
+        <v>418.34</v>
       </c>
       <c r="F13" s="4">
-        <v>491.328497909044</v>
+        <v>378.51</v>
       </c>
       <c r="G13" s="4">
-        <v>479.771178832867</v>
+        <v>356.21</v>
       </c>
       <c r="H13" s="4">
-        <v>453.208680454525</v>
+        <v>350.49</v>
       </c>
       <c r="I13" s="4">
-        <v>458.819491759793</v>
+        <v>362.97</v>
       </c>
       <c r="J13" s="4">
-        <v>440.684725061091</v>
+        <v>368.75</v>
       </c>
       <c r="K13" s="4">
-        <v>450.630291098853</v>
+        <v>405.94</v>
       </c>
       <c r="L13" s="4">
-        <v>449.545558758376</v>
+        <v>442.61</v>
       </c>
       <c r="M13" s="4">
-        <v>443.307753133256</v>
+        <v>453.9</v>
       </c>
       <c r="N13" s="4">
-        <v>450.702743528237</v>
+        <v>470.3</v>
       </c>
       <c r="O13" s="4">
-        <v>457.440291665313</v>
+        <v>445.53</v>
       </c>
       <c r="P13" s="4">
-        <v>500.369109924276</v>
+        <v>522.84</v>
       </c>
       <c r="Q13" s="4">
-        <v>499.777960298721</v>
+        <v>525.13</v>
       </c>
       <c r="R13" s="4">
-        <v>505.471132302952</v>
+        <v>553.4</v>
       </c>
       <c r="S13" s="4">
-        <v>507.356049415066</v>
+        <v>592.73</v>
       </c>
       <c r="T13" s="4">
-        <v>512.602125548294</v>
+        <v>565.96</v>
       </c>
       <c r="U13" s="4">
-        <v>670.17531627165</v>
+        <v>542.61</v>
       </c>
       <c r="V13" s="4">
-        <v>726.616402331308</v>
+        <v>595.04</v>
       </c>
       <c r="W13" s="4">
-        <v>704.501443943479</v>
+        <v>543.35</v>
       </c>
       <c r="X13" s="4">
-        <v>711.27837536407</v>
+        <v>528.3</v>
       </c>
       <c r="Y13" s="4">
-        <v>699.133615647713</v>
+        <v>492.98</v>
       </c>
       <c r="Z13" s="4">
-        <v>625.535906028361</v>
+        <v>433.46</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" customFormat="1" spans="1:26">
       <c r="A14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>499.549823348457</v>
+        <v>472.64</v>
       </c>
       <c r="D14" s="4">
-        <v>488.346401846618</v>
+        <v>453.59</v>
       </c>
       <c r="E14" s="4">
-        <v>483.962575312921</v>
+        <v>433.58</v>
       </c>
       <c r="F14" s="4">
-        <v>449.806656353734</v>
+        <v>391.31</v>
       </c>
       <c r="G14" s="4">
-        <v>429.660390298135</v>
+        <v>369.78</v>
       </c>
       <c r="H14" s="4">
-        <v>405.640994968414</v>
+        <v>368.88</v>
       </c>
       <c r="I14" s="4">
-        <v>407.804620385826</v>
+        <v>384.72</v>
       </c>
       <c r="J14" s="4">
-        <v>368.978452340737</v>
+        <v>366.79</v>
       </c>
       <c r="K14" s="4">
-        <v>386.924895789642</v>
+        <v>419.34</v>
       </c>
       <c r="L14" s="4">
-        <v>384.361960921258</v>
+        <v>461.35</v>
       </c>
       <c r="M14" s="4">
-        <v>369.35244904694</v>
+        <v>469.29</v>
       </c>
       <c r="N14" s="4">
-        <v>374.485566433404</v>
+        <v>474.03</v>
       </c>
       <c r="O14" s="4">
-        <v>370.871255819542</v>
+        <v>443.77</v>
       </c>
       <c r="P14" s="4">
-        <v>442.360747950341</v>
+        <v>525</v>
       </c>
       <c r="Q14" s="4">
-        <v>451.06694040604</v>
+        <v>526.07</v>
       </c>
       <c r="R14" s="4">
-        <v>463.727348223316</v>
+        <v>548.97</v>
       </c>
       <c r="S14" s="4">
-        <v>554.494460374124</v>
+        <v>616.9</v>
       </c>
       <c r="T14" s="4">
-        <v>533.405660109902</v>
+        <v>592.14</v>
       </c>
       <c r="U14" s="4">
-        <v>504.77001477848</v>
+        <v>559.19</v>
       </c>
       <c r="V14" s="4">
-        <v>598.285013548556</v>
+        <v>598.12</v>
       </c>
       <c r="W14" s="4">
-        <v>575.606838083591</v>
+        <v>560.02</v>
       </c>
       <c r="X14" s="4">
-        <v>561.767677780796</v>
+        <v>531.88</v>
       </c>
       <c r="Y14" s="4">
-        <v>540.771977699468</v>
+        <v>527.25</v>
       </c>
       <c r="Z14" s="4">
-        <v>454.819012387876</v>
+        <v>454.18</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:26">
       <c r="A15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="4">
-        <v>472.536298366511</v>
+        <v>353.42</v>
       </c>
       <c r="D15" s="4">
-        <v>442.293178701447</v>
+        <v>357.22</v>
       </c>
       <c r="E15" s="4">
-        <v>418.460641349833</v>
+        <v>352.15</v>
       </c>
       <c r="F15" s="4">
-        <v>379.729343526385</v>
+        <v>350.43</v>
       </c>
       <c r="G15" s="4">
-        <v>357.554449806281</v>
+        <v>332.46</v>
       </c>
       <c r="H15" s="4">
-        <v>351.164760507691</v>
+        <v>332.42</v>
       </c>
       <c r="I15" s="4">
-        <v>361.143339972786</v>
+        <v>351.07</v>
       </c>
       <c r="J15" s="4">
-        <v>364.937574958979</v>
+        <v>343.14</v>
       </c>
       <c r="K15" s="4">
-        <v>405.977722122311</v>
+        <v>369.32</v>
       </c>
       <c r="L15" s="4">
-        <v>452.11729011174</v>
+        <v>381.15</v>
       </c>
       <c r="M15" s="4">
-        <v>457.388888167619</v>
+        <v>363.67</v>
       </c>
       <c r="N15" s="4">
-        <v>480.602767594395</v>
+        <v>367.44</v>
       </c>
       <c r="O15" s="4">
-        <v>442.049464183192</v>
+        <v>356.65</v>
       </c>
       <c r="P15" s="4">
-        <v>516.080015152285</v>
+        <v>372.4</v>
       </c>
       <c r="Q15" s="4">
-        <v>521.018410335694</v>
+        <v>397.36</v>
       </c>
       <c r="R15" s="4">
-        <v>556.661451904382</v>
+        <v>409.2</v>
       </c>
       <c r="S15" s="4">
-        <v>597.299244482497</v>
+        <v>495.52</v>
       </c>
       <c r="T15" s="4">
-        <v>570.747913284065</v>
+        <v>491.63</v>
       </c>
       <c r="U15" s="4">
-        <v>546.225376926151</v>
+        <v>446.2</v>
       </c>
       <c r="V15" s="4">
-        <v>596.900991390524</v>
+        <v>534.08</v>
       </c>
       <c r="W15" s="4">
-        <v>543.781405729068</v>
+        <v>487.66</v>
       </c>
       <c r="X15" s="4">
-        <v>526.970379771097</v>
+        <v>452.58</v>
       </c>
       <c r="Y15" s="4">
-        <v>501.73994375129</v>
+        <v>404.94</v>
       </c>
       <c r="Z15" s="4">
-        <v>441.077095838014</v>
+        <v>383.07</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:26">
       <c r="A16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="4">
-        <v>472.643909385578</v>
+        <v>378.69</v>
       </c>
       <c r="D16" s="4">
-        <v>453.594710014028</v>
+        <v>378.52</v>
       </c>
       <c r="E16" s="4">
-        <v>433.57755720157</v>
+        <v>367.16</v>
       </c>
       <c r="F16" s="4">
-        <v>391.305459734486</v>
+        <v>357.27</v>
       </c>
       <c r="G16" s="4">
-        <v>369.780193515868</v>
+        <v>344.14</v>
       </c>
       <c r="H16" s="4">
-        <v>368.88069597806</v>
+        <v>343.42</v>
       </c>
       <c r="I16" s="4">
-        <v>384.722219736534</v>
+        <v>356.84</v>
       </c>
       <c r="J16" s="4">
-        <v>366.790835033589</v>
+        <v>345.91</v>
       </c>
       <c r="K16" s="4">
-        <v>419.343623000763</v>
+        <v>364.58</v>
       </c>
       <c r="L16" s="4">
-        <v>461.353912245848</v>
+        <v>396.81</v>
       </c>
       <c r="M16" s="4">
-        <v>469.2880318489</v>
+        <v>355.12</v>
       </c>
       <c r="N16" s="4">
-        <v>474.025532960201</v>
+        <v>353.05</v>
       </c>
       <c r="O16" s="4">
-        <v>443.770464668559</v>
+        <v>339.31</v>
       </c>
       <c r="P16" s="4">
-        <v>524.999392889359</v>
+        <v>366.26</v>
       </c>
       <c r="Q16" s="4">
-        <v>526.071441900764</v>
+        <v>375.84</v>
       </c>
       <c r="R16" s="4">
-        <v>548.972625456388</v>
+        <v>392.79</v>
       </c>
       <c r="S16" s="4">
-        <v>616.9049512091</v>
+        <v>452.77</v>
       </c>
       <c r="T16" s="4">
-        <v>592.135434022588</v>
+        <v>456.73</v>
       </c>
       <c r="U16" s="4">
-        <v>559.185423874112</v>
+        <v>437.58</v>
       </c>
       <c r="V16" s="4">
-        <v>598.11762282774</v>
+        <v>534.2</v>
       </c>
       <c r="W16" s="4">
-        <v>560.023574073716</v>
+        <v>473.86</v>
       </c>
       <c r="X16" s="4">
-        <v>531.883852636723</v>
+        <v>464.09</v>
       </c>
       <c r="Y16" s="4">
-        <v>527.250120571998</v>
+        <v>413.4</v>
       </c>
       <c r="Z16" s="4">
-        <v>454.183006631962</v>
+        <v>383.94</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:26">
       <c r="A17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="4">
-        <v>395.71</v>
+        <v>399.93</v>
       </c>
       <c r="D17" s="4">
-        <v>361.42</v>
+        <v>382.37</v>
       </c>
       <c r="E17" s="4">
-        <v>364.55</v>
+        <v>367.18</v>
       </c>
       <c r="F17" s="4">
-        <v>338.27</v>
+        <v>357.91</v>
       </c>
       <c r="G17" s="4">
-        <v>321.51</v>
+        <v>351.33</v>
       </c>
       <c r="H17" s="4">
-        <v>311.52</v>
+        <v>354.56</v>
       </c>
       <c r="I17" s="4">
-        <v>330.85</v>
+        <v>354.58</v>
       </c>
       <c r="J17" s="4">
-        <v>317.75</v>
+        <v>344.16</v>
       </c>
       <c r="K17" s="4">
-        <v>353.04</v>
+        <v>383.88</v>
       </c>
       <c r="L17" s="4">
-        <v>374.19</v>
+        <v>410.91</v>
       </c>
       <c r="M17" s="4">
-        <v>357.08</v>
+        <v>378.87</v>
       </c>
       <c r="N17" s="4">
-        <v>357.81</v>
+        <v>379.58</v>
       </c>
       <c r="O17" s="4">
-        <v>346.08</v>
+        <v>350.35</v>
       </c>
       <c r="P17" s="4">
-        <v>407.3</v>
+        <v>389.36</v>
       </c>
       <c r="Q17" s="4">
-        <v>401.27</v>
+        <v>399.91</v>
       </c>
       <c r="R17" s="4">
-        <v>438.43</v>
+        <v>421.26</v>
       </c>
       <c r="S17" s="4">
-        <v>517.63</v>
+        <v>484.12</v>
       </c>
       <c r="T17" s="4">
-        <v>474.02</v>
+        <v>499</v>
       </c>
       <c r="U17" s="4">
-        <v>460.9</v>
+        <v>476.21</v>
       </c>
       <c r="V17" s="4">
-        <v>549.47</v>
+        <v>569.96</v>
       </c>
       <c r="W17" s="4">
-        <v>496.43</v>
+        <v>508.7</v>
       </c>
       <c r="X17" s="4">
-        <v>479.61</v>
+        <v>473.72</v>
       </c>
       <c r="Y17" s="4">
-        <v>446.47</v>
+        <v>424.11</v>
       </c>
       <c r="Z17" s="4">
-        <v>392.77</v>
+        <v>373.49</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="A18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="4">
-        <v>378.072939628393</v>
+        <v>433.46</v>
       </c>
       <c r="D18" s="4">
-        <v>370.913220981877</v>
+        <v>419.47</v>
       </c>
       <c r="E18" s="4">
-        <v>350.158879419133</v>
+        <v>405.87</v>
       </c>
       <c r="F18" s="4">
-        <v>340.680076072717</v>
+        <v>388.55</v>
       </c>
       <c r="G18" s="4">
-        <v>340.91254898401</v>
+        <v>369.2</v>
       </c>
       <c r="H18" s="4">
-        <v>343.92367874255</v>
+        <v>372.18</v>
       </c>
       <c r="I18" s="4">
-        <v>342.335464860256</v>
+        <v>364.61</v>
       </c>
       <c r="J18" s="4">
-        <v>339.062566869322</v>
+        <v>340.46</v>
       </c>
       <c r="K18" s="4">
-        <v>352.531349808055</v>
+        <v>381.14</v>
       </c>
       <c r="L18" s="4">
-        <v>365.331175152831</v>
+        <v>407.83</v>
       </c>
       <c r="M18" s="4">
-        <v>361.103908350326</v>
+        <v>390.78</v>
       </c>
       <c r="N18" s="4">
-        <v>370.149765453412</v>
+        <v>396.8</v>
       </c>
       <c r="O18" s="4">
-        <v>348.572609456131</v>
+        <v>405.31</v>
       </c>
       <c r="P18" s="4">
-        <v>394.43004629552</v>
+        <v>429.76</v>
       </c>
       <c r="Q18" s="4">
-        <v>392.904608392072</v>
+        <v>411.92</v>
       </c>
       <c r="R18" s="4">
-        <v>437.125216039981</v>
+        <v>426.45</v>
       </c>
       <c r="S18" s="4">
-        <v>492.069867546654</v>
+        <v>475.76</v>
       </c>
       <c r="T18" s="4">
-        <v>485.015107075795</v>
+        <v>477.97</v>
       </c>
       <c r="U18" s="4">
-        <v>502.887541582654</v>
+        <v>437.7</v>
       </c>
       <c r="V18" s="4">
-        <v>607.123979504454</v>
+        <v>495.87</v>
       </c>
       <c r="W18" s="4">
-        <v>545.491505446675</v>
+        <v>467.84</v>
       </c>
       <c r="X18" s="4">
-        <v>510.106228226552</v>
+        <v>462.2</v>
       </c>
       <c r="Y18" s="4">
-        <v>476.777628434456</v>
+        <v>454.83</v>
       </c>
       <c r="Z18" s="4">
-        <v>432.639135899025</v>
+        <v>395.8</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:26">
       <c r="A19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
+        <v>41</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C19" s="4">
-        <v>380.805758119525</v>
+        <v>440.08</v>
       </c>
       <c r="D19" s="4">
-        <v>373.578846780217</v>
+        <v>418.72</v>
       </c>
       <c r="E19" s="4">
-        <v>357.297633901751</v>
+        <v>400.19</v>
       </c>
       <c r="F19" s="4">
-        <v>347.48308376995</v>
+        <v>382.22</v>
       </c>
       <c r="G19" s="4">
-        <v>346.867324417275</v>
+        <v>367.67</v>
       </c>
       <c r="H19" s="4">
-        <v>345.801602123749</v>
+        <v>369.85</v>
       </c>
       <c r="I19" s="4">
-        <v>347.214156454185</v>
+        <v>355.27</v>
       </c>
       <c r="J19" s="4">
-        <v>342.551811788602</v>
+        <v>338.06</v>
       </c>
       <c r="K19" s="4">
-        <v>355.122312012989</v>
+        <v>355.6</v>
       </c>
       <c r="L19" s="4">
-        <v>367.776109788426</v>
+        <v>381.02</v>
       </c>
       <c r="M19" s="4">
-        <v>367.099675246369</v>
+        <v>387.82</v>
       </c>
       <c r="N19" s="4">
-        <v>373.210642054964</v>
+        <v>389.31</v>
       </c>
       <c r="O19" s="4">
-        <v>353.025070654336</v>
+        <v>406.67</v>
       </c>
       <c r="P19" s="4">
-        <v>394.43004629552</v>
+        <v>428.58</v>
       </c>
       <c r="Q19" s="4">
-        <v>394.341838133525</v>
+        <v>393.23</v>
       </c>
       <c r="R19" s="4">
-        <v>437.125216039981</v>
+        <v>390.6</v>
       </c>
       <c r="S19" s="4">
-        <v>492.069867546654</v>
+        <v>436.49</v>
       </c>
       <c r="T19" s="4">
-        <v>488.97576206992</v>
+        <v>441.77</v>
       </c>
       <c r="U19" s="4">
-        <v>506.477831957841</v>
+        <v>407.47</v>
       </c>
       <c r="V19" s="4">
-        <v>609.689416465988</v>
+        <v>441.42</v>
       </c>
       <c r="W19" s="4">
-        <v>547.597940856486</v>
+        <v>437.06</v>
       </c>
       <c r="X19" s="4">
-        <v>516.253494592302</v>
+        <v>429.59</v>
       </c>
       <c r="Y19" s="4">
-        <v>481.684634660761</v>
+        <v>417.69</v>
       </c>
       <c r="Z19" s="4">
-        <v>434.858421074339</v>
+        <v>388.94</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:26">
       <c r="A20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="4">
-        <v>388.202730542476</v>
+        <v>408.6</v>
       </c>
       <c r="D20" s="4">
-        <v>392.737073553957</v>
+        <v>396.55</v>
       </c>
       <c r="E20" s="4">
-        <v>377.404615127363</v>
+        <v>386.89</v>
       </c>
       <c r="F20" s="4">
-        <v>379.972109581057</v>
+        <v>381.95</v>
       </c>
       <c r="G20" s="4">
-        <v>365.620315887356</v>
+        <v>364.56</v>
       </c>
       <c r="H20" s="4">
-        <v>370.931177453823</v>
+        <v>369.22</v>
       </c>
       <c r="I20" s="4">
-        <v>367.365636149892</v>
+        <v>373.39</v>
       </c>
       <c r="J20" s="4">
-        <v>353.951475591681</v>
+        <v>377.18</v>
       </c>
       <c r="K20" s="4">
-        <v>392.55742788183</v>
+        <v>434.71</v>
       </c>
       <c r="L20" s="4">
-        <v>407.945537486317</v>
+        <v>495.86</v>
       </c>
       <c r="M20" s="4">
-        <v>387.496009377131</v>
+        <v>486.17</v>
       </c>
       <c r="N20" s="4">
-        <v>393.647372856362</v>
+        <v>504.16</v>
       </c>
       <c r="O20" s="4">
-        <v>376.884285401997</v>
+        <v>501.73</v>
       </c>
       <c r="P20" s="4">
-        <v>392.912747716845</v>
+        <v>541.41</v>
       </c>
       <c r="Q20" s="4">
-        <v>401.737445267995</v>
+        <v>503.33</v>
       </c>
       <c r="R20" s="4">
-        <v>415.806789729676</v>
+        <v>519.2</v>
       </c>
       <c r="S20" s="4">
-        <v>480.694310831758</v>
+        <v>566.33</v>
       </c>
       <c r="T20" s="4">
-        <v>485.011688657326</v>
+        <v>558.98</v>
       </c>
       <c r="U20" s="4">
-        <v>510.579394473448</v>
+        <v>494.96</v>
       </c>
       <c r="V20" s="4">
-        <v>608.314859185175</v>
+        <v>549.69</v>
       </c>
       <c r="W20" s="4">
-        <v>545.225274308285</v>
+        <v>509.03</v>
       </c>
       <c r="X20" s="4">
-        <v>520.384944056136</v>
+        <v>475.8</v>
       </c>
       <c r="Y20" s="4">
-        <v>470.222375215246</v>
+        <v>453.21</v>
       </c>
       <c r="Z20" s="4">
-        <v>429.712100589911</v>
+        <v>396.92</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:26">
       <c r="A21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="4">
-        <v>448.85</v>
+        <v>430.03</v>
       </c>
       <c r="D21" s="4">
-        <v>432.14</v>
+        <v>421.26</v>
       </c>
       <c r="E21" s="4">
-        <v>407.11</v>
+        <v>403.28</v>
       </c>
       <c r="F21" s="4">
-        <v>392.68</v>
+        <v>392.76</v>
       </c>
       <c r="G21" s="4">
-        <v>375.48</v>
+        <v>362.13</v>
       </c>
       <c r="H21" s="4">
-        <v>375.84</v>
+        <v>368.46</v>
       </c>
       <c r="I21" s="4">
-        <v>375.23</v>
+        <v>367.03</v>
       </c>
       <c r="J21" s="4">
-        <v>352.01</v>
+        <v>364.65</v>
       </c>
       <c r="K21" s="4">
-        <v>379.48</v>
+        <v>436.82</v>
       </c>
       <c r="L21" s="4">
-        <v>416.92</v>
+        <v>490.4</v>
       </c>
       <c r="M21" s="4">
-        <v>395.9</v>
+        <v>471.9</v>
       </c>
       <c r="N21" s="4">
-        <v>408.56</v>
+        <v>471.59</v>
       </c>
       <c r="O21" s="4">
-        <v>391.77</v>
+        <v>467.6</v>
       </c>
       <c r="P21" s="4">
-        <v>430.21</v>
+        <v>500.17</v>
       </c>
       <c r="Q21" s="4">
-        <v>424.86</v>
+        <v>474.79</v>
       </c>
       <c r="R21" s="4">
-        <v>441.59</v>
+        <v>496.79</v>
       </c>
       <c r="S21" s="4">
-        <v>492.17</v>
+        <v>556.09</v>
       </c>
       <c r="T21" s="4">
-        <v>496.32</v>
+        <v>554.91</v>
       </c>
       <c r="U21" s="4">
-        <v>459.16</v>
+        <v>506.12</v>
       </c>
       <c r="V21" s="4">
-        <v>538.34</v>
+        <v>568.37</v>
       </c>
       <c r="W21" s="4">
-        <v>507.39</v>
+        <v>520.24</v>
       </c>
       <c r="X21" s="4">
-        <v>497.35</v>
+        <v>500.63</v>
       </c>
       <c r="Y21" s="4">
-        <v>468.25</v>
+        <v>463.77</v>
       </c>
       <c r="Z21" s="4">
-        <v>415.64</v>
+        <v>409.69</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="A22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
+        <v>44</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C22" s="4">
-        <v>448.79</v>
+        <v>407.9</v>
       </c>
       <c r="D22" s="4">
-        <v>432.14</v>
+        <v>398.09</v>
       </c>
       <c r="E22" s="4">
-        <v>410.77</v>
+        <v>392.23</v>
       </c>
       <c r="F22" s="4">
-        <v>395.01</v>
+        <v>382.99</v>
       </c>
       <c r="G22" s="4">
-        <v>376.18</v>
+        <v>380.27</v>
       </c>
       <c r="H22" s="4">
-        <v>376.16</v>
+        <v>376.15</v>
       </c>
       <c r="I22" s="4">
-        <v>375.45</v>
+        <v>380.96</v>
       </c>
       <c r="J22" s="4">
-        <v>351.61</v>
+        <v>379.6</v>
       </c>
       <c r="K22" s="4">
-        <v>379.48</v>
+        <v>417.98</v>
       </c>
       <c r="L22" s="4">
-        <v>416.92</v>
+        <v>446.51</v>
       </c>
       <c r="M22" s="4">
-        <v>395.9</v>
+        <v>424.44</v>
       </c>
       <c r="N22" s="4">
-        <v>408.56</v>
+        <v>425.15</v>
       </c>
       <c r="O22" s="4">
-        <v>391.77</v>
+        <v>416.57</v>
       </c>
       <c r="P22" s="4">
-        <v>428.54</v>
+        <v>451.35</v>
       </c>
       <c r="Q22" s="4">
-        <v>424.11</v>
+        <v>431.35</v>
       </c>
       <c r="R22" s="4">
-        <v>441.59</v>
+        <v>465.85</v>
       </c>
       <c r="S22" s="4">
-        <v>492.17</v>
+        <v>488.31</v>
       </c>
       <c r="T22" s="4">
-        <v>496.32</v>
+        <v>490.88</v>
       </c>
       <c r="U22" s="4">
-        <v>459.44</v>
+        <v>456.72</v>
       </c>
       <c r="V22" s="4">
-        <v>538.34</v>
+        <v>505.04</v>
       </c>
       <c r="W22" s="4">
-        <v>507.39</v>
+        <v>466.81</v>
       </c>
       <c r="X22" s="4">
-        <v>499.4</v>
+        <v>456.94</v>
       </c>
       <c r="Y22" s="4">
-        <v>473.86</v>
+        <v>423.83</v>
       </c>
       <c r="Z22" s="4">
-        <v>416.23</v>
+        <v>381.92</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:26">
       <c r="A23" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="4">
-        <v>441.58</v>
+        <v>371.02</v>
       </c>
       <c r="D23" s="4">
-        <v>416.82</v>
+        <v>356.22</v>
       </c>
       <c r="E23" s="4">
-        <v>400.59</v>
+        <v>337.16</v>
       </c>
       <c r="F23" s="4">
+        <v>340.41</v>
+      </c>
+      <c r="G23" s="4">
+        <v>330.2</v>
+      </c>
+      <c r="H23" s="4">
+        <v>325.92</v>
+      </c>
+      <c r="I23" s="4">
+        <v>325.87</v>
+      </c>
+      <c r="J23" s="4">
+        <v>326.66</v>
+      </c>
+      <c r="K23" s="4">
         <v>382.56</v>
       </c>
-      <c r="G23" s="4">
-        <v>369.17</v>
-      </c>
-      <c r="H23" s="4">
-        <v>370.27</v>
-      </c>
-      <c r="I23" s="4">
-        <v>359.27</v>
-      </c>
-      <c r="J23" s="4">
-        <v>345.84</v>
-      </c>
-      <c r="K23" s="4">
-        <v>350.84</v>
-      </c>
       <c r="L23" s="4">
-        <v>380.34</v>
+        <v>428.04</v>
       </c>
       <c r="M23" s="4">
-        <v>384.74</v>
+        <v>421.52</v>
       </c>
       <c r="N23" s="4">
-        <v>388.74</v>
+        <v>425.04</v>
       </c>
       <c r="O23" s="4">
-        <v>375.28</v>
+        <v>406.95</v>
       </c>
       <c r="P23" s="4">
-        <v>412.23</v>
+        <v>428.68</v>
       </c>
       <c r="Q23" s="4">
-        <v>390.47</v>
+        <v>396.82</v>
       </c>
       <c r="R23" s="4">
-        <v>394.2</v>
+        <v>408.32</v>
       </c>
       <c r="S23" s="4">
-        <v>418.68</v>
+        <v>431.91</v>
       </c>
       <c r="T23" s="4">
-        <v>441.73</v>
+        <v>411.41</v>
       </c>
       <c r="U23" s="4">
-        <v>412.57</v>
+        <v>362.75</v>
       </c>
       <c r="V23" s="4">
-        <v>477.14</v>
+        <v>422.12</v>
       </c>
       <c r="W23" s="4">
-        <v>457.3</v>
+        <v>397.75</v>
       </c>
       <c r="X23" s="4">
-        <v>451.62</v>
+        <v>386.87</v>
       </c>
       <c r="Y23" s="4">
-        <v>423.55</v>
+        <v>363.3</v>
       </c>
       <c r="Z23" s="4">
-        <v>377.56</v>
+        <v>341.18</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
+        <v>46</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C24" s="4">
-        <v>441.81</v>
+        <v>397.87</v>
       </c>
       <c r="D24" s="4">
-        <v>416.82</v>
+        <v>367.66</v>
       </c>
       <c r="E24" s="4">
-        <v>403.27</v>
+        <v>338.64</v>
       </c>
       <c r="F24" s="4">
-        <v>383.89</v>
+        <v>302.5</v>
       </c>
       <c r="G24" s="4">
-        <v>369.21</v>
+        <v>290.38</v>
       </c>
       <c r="H24" s="4">
-        <v>370.46</v>
+        <v>280.17</v>
       </c>
       <c r="I24" s="4">
-        <v>359.29</v>
+        <v>277.78</v>
       </c>
       <c r="J24" s="4">
-        <v>345.34</v>
+        <v>246.01</v>
       </c>
       <c r="K24" s="4">
-        <v>350.84</v>
+        <v>246.02</v>
       </c>
       <c r="L24" s="4">
-        <v>380.34</v>
+        <v>212.56</v>
       </c>
       <c r="M24" s="4">
-        <v>384.74</v>
+        <v>194.77</v>
       </c>
       <c r="N24" s="4">
-        <v>388.74</v>
+        <v>201.5</v>
       </c>
       <c r="O24" s="4">
-        <v>375.28</v>
+        <v>168.3</v>
       </c>
       <c r="P24" s="4">
-        <v>411.63</v>
+        <v>216.44</v>
       </c>
       <c r="Q24" s="4">
-        <v>389.55</v>
+        <v>222.08</v>
       </c>
       <c r="R24" s="4">
-        <v>394.2</v>
+        <v>198.69</v>
       </c>
       <c r="S24" s="4">
-        <v>418.68</v>
+        <v>229.92</v>
       </c>
       <c r="T24" s="4">
-        <v>441.73</v>
+        <v>262.75</v>
       </c>
       <c r="U24" s="4">
-        <v>412.71</v>
+        <v>292.37</v>
       </c>
       <c r="V24" s="4">
-        <v>477.14</v>
+        <v>294.33</v>
       </c>
       <c r="W24" s="4">
-        <v>457.3</v>
+        <v>297.88</v>
       </c>
       <c r="X24" s="4">
-        <v>455.33</v>
+        <v>280.96</v>
       </c>
       <c r="Y24" s="4">
-        <v>428.95</v>
+        <v>280.59</v>
       </c>
       <c r="Z24" s="4">
-        <v>377.92</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:26">
-      <c r="A25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="4">
-        <v>393.82</v>
-      </c>
-      <c r="D25" s="4">
-        <v>382.09</v>
-      </c>
-      <c r="E25" s="4">
-        <v>373.63</v>
-      </c>
-      <c r="F25" s="4">
-        <v>371.44</v>
-      </c>
-      <c r="G25" s="4">
-        <v>353.25</v>
-      </c>
-      <c r="H25" s="4">
-        <v>355.8</v>
-      </c>
-      <c r="I25" s="4">
-        <v>367.67</v>
-      </c>
-      <c r="J25" s="4">
-        <v>370.23</v>
-      </c>
-      <c r="K25" s="4">
-        <v>425.26</v>
-      </c>
-      <c r="L25" s="4">
-        <v>474.38</v>
-      </c>
-      <c r="M25" s="4">
-        <v>458.86</v>
-      </c>
-      <c r="N25" s="4">
-        <v>478.82</v>
-      </c>
-      <c r="O25" s="4">
-        <v>449.94</v>
-      </c>
-      <c r="P25" s="4">
-        <v>500.78</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>486.63</v>
-      </c>
-      <c r="R25" s="4">
-        <v>500.37</v>
-      </c>
-      <c r="S25" s="4">
-        <v>549.2</v>
-      </c>
-      <c r="T25" s="4">
-        <v>540.96</v>
-      </c>
-      <c r="U25" s="4">
-        <v>492.61</v>
-      </c>
-      <c r="V25" s="4">
-        <v>587.13</v>
-      </c>
-      <c r="W25" s="4">
-        <v>530.93</v>
-      </c>
-      <c r="X25" s="4">
-        <v>484.88</v>
-      </c>
-      <c r="Y25" s="4">
-        <v>450.5</v>
-      </c>
-      <c r="Z25" s="4">
-        <v>386.19</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:26">
-      <c r="A26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="4">
-        <v>393.94</v>
-      </c>
-      <c r="D26" s="4">
-        <v>382.09</v>
-      </c>
-      <c r="E26" s="4">
-        <v>376.9</v>
-      </c>
-      <c r="F26" s="4">
-        <v>373.55</v>
-      </c>
-      <c r="G26" s="4">
-        <v>353.75</v>
-      </c>
-      <c r="H26" s="4">
-        <v>356.07</v>
-      </c>
-      <c r="I26" s="4">
-        <v>367.78</v>
-      </c>
-      <c r="J26" s="4">
-        <v>369.71</v>
-      </c>
-      <c r="K26" s="4">
-        <v>425.26</v>
-      </c>
-      <c r="L26" s="4">
-        <v>474.38</v>
-      </c>
-      <c r="M26" s="4">
-        <v>458.86</v>
-      </c>
-      <c r="N26" s="4">
-        <v>478.82</v>
-      </c>
-      <c r="O26" s="4">
-        <v>449.94</v>
-      </c>
-      <c r="P26" s="4">
-        <v>499.45</v>
-      </c>
-      <c r="Q26" s="4">
-        <v>485.73</v>
-      </c>
-      <c r="R26" s="4">
-        <v>500.37</v>
-      </c>
-      <c r="S26" s="4">
-        <v>549.2</v>
-      </c>
-      <c r="T26" s="4">
-        <v>540.96</v>
-      </c>
-      <c r="U26" s="4">
-        <v>492.58</v>
-      </c>
-      <c r="V26" s="4">
-        <v>587.13</v>
-      </c>
-      <c r="W26" s="4">
-        <v>530.93</v>
-      </c>
-      <c r="X26" s="4">
-        <v>488.24</v>
-      </c>
-      <c r="Y26" s="4">
-        <v>456.11</v>
-      </c>
-      <c r="Z26" s="4">
-        <v>386.67</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:26">
-      <c r="A27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="4">
-        <v>433.25</v>
-      </c>
-      <c r="D27" s="4">
-        <v>419.74</v>
-      </c>
-      <c r="E27" s="4">
-        <v>396.44</v>
-      </c>
-      <c r="F27" s="4">
-        <v>391.43</v>
-      </c>
-      <c r="G27" s="4">
-        <v>362.52</v>
-      </c>
-      <c r="H27" s="4">
-        <v>369.54</v>
-      </c>
-      <c r="I27" s="4">
-        <v>373.27</v>
-      </c>
-      <c r="J27" s="4">
-        <v>371.32</v>
-      </c>
-      <c r="K27" s="4">
-        <v>439.79</v>
-      </c>
-      <c r="L27" s="4">
-        <v>489.58</v>
-      </c>
-      <c r="M27" s="4">
-        <v>478.5</v>
-      </c>
-      <c r="N27" s="4">
-        <v>476.74</v>
-      </c>
-      <c r="O27" s="4">
-        <v>448.32</v>
-      </c>
-      <c r="P27" s="4">
-        <v>498.11</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>475.62</v>
-      </c>
-      <c r="R27" s="4">
-        <v>500.24</v>
-      </c>
-      <c r="S27" s="4">
-        <v>566.01</v>
-      </c>
-      <c r="T27" s="4">
-        <v>566.02</v>
-      </c>
-      <c r="U27" s="4">
-        <v>519.67</v>
-      </c>
-      <c r="V27" s="4">
-        <v>622.73</v>
-      </c>
-      <c r="W27" s="4">
-        <v>566.61</v>
-      </c>
-      <c r="X27" s="4">
-        <v>528.61</v>
-      </c>
-      <c r="Y27" s="4">
-        <v>472.16</v>
-      </c>
-      <c r="Z27" s="4">
-        <v>410.04</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:26">
-      <c r="A28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4">
-        <v>396.34</v>
-      </c>
-      <c r="D28" s="4">
-        <v>381.1</v>
-      </c>
-      <c r="E28" s="4">
-        <v>372.69</v>
-      </c>
-      <c r="F28" s="4">
-        <v>367.09</v>
-      </c>
-      <c r="G28" s="4">
-        <v>359.03</v>
-      </c>
-      <c r="H28" s="4">
-        <v>356.59</v>
-      </c>
-      <c r="I28" s="4">
-        <v>365.66</v>
-      </c>
-      <c r="J28" s="4">
-        <v>365.99</v>
-      </c>
-      <c r="K28" s="4">
-        <v>405.73</v>
-      </c>
-      <c r="L28" s="4">
-        <v>439.57</v>
-      </c>
-      <c r="M28" s="4">
-        <v>418.75</v>
-      </c>
-      <c r="N28" s="4">
-        <v>430.5</v>
-      </c>
-      <c r="O28" s="4">
-        <v>404.26</v>
-      </c>
-      <c r="P28" s="4">
-        <v>456.27</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>429.36</v>
-      </c>
-      <c r="R28" s="4">
-        <v>470.38</v>
-      </c>
-      <c r="S28" s="4">
-        <v>505.13</v>
-      </c>
-      <c r="T28" s="4">
-        <v>512.47</v>
-      </c>
-      <c r="U28" s="4">
-        <v>466.19</v>
-      </c>
-      <c r="V28" s="4">
-        <v>562.67</v>
-      </c>
-      <c r="W28" s="4">
-        <v>490.05</v>
-      </c>
-      <c r="X28" s="4">
-        <v>465.2</v>
-      </c>
-      <c r="Y28" s="4">
-        <v>411.23</v>
-      </c>
-      <c r="Z28" s="4">
-        <v>364.92</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:26">
-      <c r="A29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="4">
-        <v>382.35</v>
-      </c>
-      <c r="D29" s="4">
-        <v>364.28</v>
-      </c>
-      <c r="E29" s="4">
-        <v>342.7</v>
-      </c>
-      <c r="F29" s="4">
-        <v>327.87</v>
-      </c>
-      <c r="G29" s="4">
-        <v>314.14</v>
-      </c>
-      <c r="H29" s="4">
-        <v>324.67</v>
-      </c>
-      <c r="I29" s="4">
-        <v>327.57</v>
-      </c>
-      <c r="J29" s="4">
-        <v>323.49</v>
-      </c>
-      <c r="K29" s="4">
-        <v>371.59</v>
-      </c>
-      <c r="L29" s="4">
-        <v>421.31</v>
-      </c>
-      <c r="M29" s="4">
-        <v>407.96</v>
-      </c>
-      <c r="N29" s="4">
-        <v>407.96</v>
-      </c>
-      <c r="O29" s="4">
-        <v>397.4</v>
-      </c>
-      <c r="P29" s="4">
-        <v>426.82</v>
-      </c>
-      <c r="Q29" s="4">
-        <v>390.89</v>
-      </c>
-      <c r="R29" s="4">
-        <v>396.16</v>
-      </c>
-      <c r="S29" s="4">
-        <v>413.86</v>
-      </c>
-      <c r="T29" s="4">
-        <v>414.41</v>
-      </c>
-      <c r="U29" s="4">
-        <v>379.5</v>
-      </c>
-      <c r="V29" s="4">
-        <v>439.34</v>
-      </c>
-      <c r="W29" s="4">
-        <v>406.75</v>
-      </c>
-      <c r="X29" s="4">
-        <v>389.85</v>
-      </c>
-      <c r="Y29" s="4">
-        <v>378.13</v>
-      </c>
-      <c r="Z29" s="4">
-        <v>333.41</v>
+        <v>289.21</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="11020"/>
+    <workbookView windowWidth="32520" windowHeight="14220"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>日期</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3089,6 +3098,246 @@
         <v>289.21</v>
       </c>
     </row>
+    <row r="25" customFormat="1" spans="1:26">
+      <c r="A25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4">
+        <v>448.46</v>
+      </c>
+      <c r="D25" s="4">
+        <v>434.81</v>
+      </c>
+      <c r="E25" s="4">
+        <v>414.01</v>
+      </c>
+      <c r="F25" s="4">
+        <v>396.27</v>
+      </c>
+      <c r="G25" s="4">
+        <v>378.03</v>
+      </c>
+      <c r="H25" s="4">
+        <v>374.02</v>
+      </c>
+      <c r="I25" s="4">
+        <v>374.31</v>
+      </c>
+      <c r="J25" s="4">
+        <v>360.12</v>
+      </c>
+      <c r="K25" s="4">
+        <v>397.32</v>
+      </c>
+      <c r="L25" s="4">
+        <v>424.35</v>
+      </c>
+      <c r="M25" s="4">
+        <v>403.91</v>
+      </c>
+      <c r="N25" s="4">
+        <v>400.95</v>
+      </c>
+      <c r="O25" s="4">
+        <v>385.27</v>
+      </c>
+      <c r="P25" s="4">
+        <v>383.73</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>410.93</v>
+      </c>
+      <c r="R25" s="4">
+        <v>422.17</v>
+      </c>
+      <c r="S25" s="4">
+        <v>441.56</v>
+      </c>
+      <c r="T25" s="4">
+        <v>469.88</v>
+      </c>
+      <c r="U25" s="4">
+        <v>459.89</v>
+      </c>
+      <c r="V25" s="4">
+        <v>494.87</v>
+      </c>
+      <c r="W25" s="4">
+        <v>471.93</v>
+      </c>
+      <c r="X25" s="4">
+        <v>476.64</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>471.78</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>439.3</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:26">
+      <c r="A26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4">
+        <v>449.92</v>
+      </c>
+      <c r="D26" s="4">
+        <v>451.42</v>
+      </c>
+      <c r="E26" s="4">
+        <v>422.94</v>
+      </c>
+      <c r="F26" s="4">
+        <v>416.72</v>
+      </c>
+      <c r="G26" s="4">
+        <v>414.69</v>
+      </c>
+      <c r="H26" s="4">
+        <v>414.77</v>
+      </c>
+      <c r="I26" s="4">
+        <v>405.31</v>
+      </c>
+      <c r="J26" s="4">
+        <v>393.55</v>
+      </c>
+      <c r="K26" s="4">
+        <v>391.6</v>
+      </c>
+      <c r="L26" s="4">
+        <v>417.52</v>
+      </c>
+      <c r="M26" s="4">
+        <v>395.35</v>
+      </c>
+      <c r="N26" s="4">
+        <v>387.56</v>
+      </c>
+      <c r="O26" s="4">
+        <v>387.08</v>
+      </c>
+      <c r="P26" s="4">
+        <v>393.45</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>393.53</v>
+      </c>
+      <c r="R26" s="4">
+        <v>423.01</v>
+      </c>
+      <c r="S26" s="4">
+        <v>437.92</v>
+      </c>
+      <c r="T26" s="4">
+        <v>453.05</v>
+      </c>
+      <c r="U26" s="4">
+        <v>434.56</v>
+      </c>
+      <c r="V26" s="4">
+        <v>467.56</v>
+      </c>
+      <c r="W26" s="4">
+        <v>460.03</v>
+      </c>
+      <c r="X26" s="4">
+        <v>464.1</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>462.61</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>419.69</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:26">
+      <c r="A27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="4">
+        <v>451.24</v>
+      </c>
+      <c r="D27" s="4">
+        <v>435.72</v>
+      </c>
+      <c r="E27" s="4">
+        <v>425.78</v>
+      </c>
+      <c r="F27" s="4">
+        <v>414.68</v>
+      </c>
+      <c r="G27" s="4">
+        <v>406.38</v>
+      </c>
+      <c r="H27" s="4">
+        <v>405.36</v>
+      </c>
+      <c r="I27" s="4">
+        <v>402.74</v>
+      </c>
+      <c r="J27" s="4">
+        <v>405.43</v>
+      </c>
+      <c r="K27" s="4">
+        <v>457.83</v>
+      </c>
+      <c r="L27" s="4">
+        <v>483.52</v>
+      </c>
+      <c r="M27" s="4">
+        <v>487.1</v>
+      </c>
+      <c r="N27" s="4">
+        <v>498.2</v>
+      </c>
+      <c r="O27" s="4">
+        <v>482.83</v>
+      </c>
+      <c r="P27" s="4">
+        <v>499.2</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>496.43</v>
+      </c>
+      <c r="R27" s="4">
+        <v>530.82</v>
+      </c>
+      <c r="S27" s="4">
+        <v>515.51</v>
+      </c>
+      <c r="T27" s="4">
+        <v>528.53</v>
+      </c>
+      <c r="U27" s="4">
+        <v>482.61</v>
+      </c>
+      <c r="V27" s="4">
+        <v>535.9</v>
+      </c>
+      <c r="W27" s="4">
+        <v>516.13</v>
+      </c>
+      <c r="X27" s="4">
+        <v>511.96</v>
+      </c>
+      <c r="Y27" s="4">
+        <v>498.87</v>
+      </c>
+      <c r="Z27" s="4">
+        <v>455.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>日期</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3338,6 +3341,86 @@
         <v>455.22</v>
       </c>
     </row>
+    <row r="28" customFormat="1" spans="1:26">
+      <c r="A28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="4">
+        <v>565.65</v>
+      </c>
+      <c r="D28" s="4">
+        <v>468.93</v>
+      </c>
+      <c r="E28" s="4">
+        <v>452.73</v>
+      </c>
+      <c r="F28" s="4">
+        <v>436.78</v>
+      </c>
+      <c r="G28" s="4">
+        <v>422.19</v>
+      </c>
+      <c r="H28" s="4">
+        <v>425.63</v>
+      </c>
+      <c r="I28" s="4">
+        <v>416.72</v>
+      </c>
+      <c r="J28" s="4">
+        <v>410.73</v>
+      </c>
+      <c r="K28" s="4">
+        <v>467.21</v>
+      </c>
+      <c r="L28" s="4">
+        <v>485.89</v>
+      </c>
+      <c r="M28" s="4">
+        <v>477.06</v>
+      </c>
+      <c r="N28" s="4">
+        <v>537.96</v>
+      </c>
+      <c r="O28" s="4">
+        <v>501.21</v>
+      </c>
+      <c r="P28" s="4">
+        <v>559.09</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>522.74</v>
+      </c>
+      <c r="R28" s="4">
+        <v>526.94</v>
+      </c>
+      <c r="S28" s="4">
+        <v>591.13</v>
+      </c>
+      <c r="T28" s="4">
+        <v>598.81</v>
+      </c>
+      <c r="U28" s="4">
+        <v>661.45</v>
+      </c>
+      <c r="V28" s="4">
+        <v>722.26</v>
+      </c>
+      <c r="W28" s="4">
+        <v>716.12</v>
+      </c>
+      <c r="X28" s="4">
+        <v>633.87</v>
+      </c>
+      <c r="Y28" s="4">
+        <v>621.11</v>
+      </c>
+      <c r="Z28" s="4">
+        <v>454.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32520" windowHeight="14220"/>
+    <workbookView windowWidth="32520" windowHeight="7440"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -3349,76 +3349,76 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>565.65</v>
+        <v>560.7</v>
       </c>
       <c r="D28" s="4">
-        <v>468.93</v>
+        <v>510.85</v>
       </c>
       <c r="E28" s="4">
-        <v>452.73</v>
+        <v>472.06</v>
       </c>
       <c r="F28" s="4">
-        <v>436.78</v>
+        <v>441.16</v>
       </c>
       <c r="G28" s="4">
-        <v>422.19</v>
+        <v>406.3</v>
       </c>
       <c r="H28" s="4">
-        <v>425.63</v>
+        <v>398.1</v>
       </c>
       <c r="I28" s="4">
-        <v>416.72</v>
+        <v>414.43</v>
       </c>
       <c r="J28" s="4">
-        <v>410.73</v>
+        <v>404.81</v>
       </c>
       <c r="K28" s="4">
-        <v>467.21</v>
+        <v>473.86</v>
       </c>
       <c r="L28" s="4">
-        <v>485.89</v>
+        <v>512.45</v>
       </c>
       <c r="M28" s="4">
-        <v>477.06</v>
+        <v>496.73</v>
       </c>
       <c r="N28" s="4">
-        <v>537.96</v>
+        <v>571.3</v>
       </c>
       <c r="O28" s="4">
-        <v>501.21</v>
+        <v>554.9</v>
       </c>
       <c r="P28" s="4">
-        <v>559.09</v>
+        <v>596.05</v>
       </c>
       <c r="Q28" s="4">
-        <v>522.74</v>
+        <v>511.08</v>
       </c>
       <c r="R28" s="4">
-        <v>526.94</v>
+        <v>556.64</v>
       </c>
       <c r="S28" s="4">
-        <v>591.13</v>
+        <v>602.19</v>
       </c>
       <c r="T28" s="4">
-        <v>598.81</v>
+        <v>632.07</v>
       </c>
       <c r="U28" s="4">
-        <v>661.45</v>
+        <v>698.55</v>
       </c>
       <c r="V28" s="4">
-        <v>722.26</v>
+        <v>757.2</v>
       </c>
       <c r="W28" s="4">
-        <v>716.12</v>
+        <v>747.78</v>
       </c>
       <c r="X28" s="4">
-        <v>633.87</v>
+        <v>666.66</v>
       </c>
       <c r="Y28" s="4">
-        <v>621.11</v>
+        <v>644.72</v>
       </c>
       <c r="Z28" s="4">
-        <v>454.54</v>
+        <v>500.39</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32520" windowHeight="7440"/>
+    <workbookView windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>日期</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2461,7 +2464,7 @@
         <v>383.94</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:26">
+    <row r="17" customFormat="1" spans="1:27">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -2541,7 +2544,7 @@
         <v>373.49</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:26">
+    <row r="18" customFormat="1" spans="1:27">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>395.8</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:26">
+    <row r="19" customFormat="1" spans="1:27">
       <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2701,7 +2704,7 @@
         <v>388.94</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:26">
+    <row r="20" customFormat="1" spans="1:27">
       <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
@@ -2781,7 +2784,7 @@
         <v>396.92</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:26">
+    <row r="21" customFormat="1" spans="1:27">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:26">
+    <row r="22" customFormat="1" spans="1:27">
       <c r="A22" s="4" t="s">
         <v>44</v>
       </c>
@@ -2941,7 +2944,7 @@
         <v>381.92</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:26">
+    <row r="23" customFormat="1" spans="1:27">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -3021,7 +3024,7 @@
         <v>341.18</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:26">
+    <row r="24" customFormat="1" spans="1:27">
       <c r="A24" s="4" t="s">
         <v>46</v>
       </c>
@@ -3101,7 +3104,7 @@
         <v>289.21</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:26">
+    <row r="25" customFormat="1" spans="1:27">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -3181,7 +3184,7 @@
         <v>439.3</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:26">
+    <row r="26" customFormat="1" spans="1:27">
       <c r="A26" s="4" t="s">
         <v>48</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>419.69</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:26">
+    <row r="27" customFormat="1" spans="1:27">
       <c r="A27" s="4" t="s">
         <v>49</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>455.22</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:26">
+    <row r="28" customFormat="1" spans="1:27">
       <c r="A28" s="4" t="s">
         <v>50</v>
       </c>
@@ -3419,6 +3422,89 @@
       </c>
       <c r="Z28" s="4">
         <v>500.39</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:27">
+      <c r="A29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4">
+        <v>549.36</v>
+      </c>
+      <c r="D29" s="4">
+        <v>500.27</v>
+      </c>
+      <c r="E29" s="4">
+        <v>461.6</v>
+      </c>
+      <c r="F29" s="4">
+        <v>433.94</v>
+      </c>
+      <c r="G29" s="4">
+        <v>402.61</v>
+      </c>
+      <c r="H29" s="4">
+        <v>393.8</v>
+      </c>
+      <c r="I29" s="4">
+        <v>409.62</v>
+      </c>
+      <c r="J29" s="4">
+        <v>398.75</v>
+      </c>
+      <c r="K29" s="4">
+        <v>464.53</v>
+      </c>
+      <c r="L29" s="4">
+        <v>504.77</v>
+      </c>
+      <c r="M29" s="4">
+        <v>492.01</v>
+      </c>
+      <c r="N29" s="4">
+        <v>562.74</v>
+      </c>
+      <c r="O29" s="4">
+        <v>553.45</v>
+      </c>
+      <c r="P29" s="4">
+        <v>586.52</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>508.23</v>
+      </c>
+      <c r="R29" s="4">
+        <v>550.73</v>
+      </c>
+      <c r="S29" s="4">
+        <v>583.9</v>
+      </c>
+      <c r="T29" s="4">
+        <v>611.85</v>
+      </c>
+      <c r="U29" s="4">
+        <v>680.19</v>
+      </c>
+      <c r="V29" s="4">
+        <v>739.27</v>
+      </c>
+      <c r="W29" s="4">
+        <v>734.86</v>
+      </c>
+      <c r="X29" s="4">
+        <v>654.85</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>634.91</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>491.06</v>
+      </c>
+      <c r="AA29">
+        <v>537.66</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -1173,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2464,7 +2464,7 @@
         <v>383.94</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:27">
+    <row r="17" customFormat="1" spans="1:26">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>373.49</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:27">
+    <row r="18" customFormat="1" spans="1:26">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>395.8</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:27">
+    <row r="19" customFormat="1" spans="1:26">
       <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>388.94</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:27">
+    <row r="20" customFormat="1" spans="1:26">
       <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>396.92</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:27">
+    <row r="21" customFormat="1" spans="1:26">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:27">
+    <row r="22" customFormat="1" spans="1:26">
       <c r="A22" s="4" t="s">
         <v>44</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>381.92</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:27">
+    <row r="23" customFormat="1" spans="1:26">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>341.18</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:27">
+    <row r="24" customFormat="1" spans="1:26">
       <c r="A24" s="4" t="s">
         <v>46</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>289.21</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:27">
+    <row r="25" customFormat="1" spans="1:26">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>439.3</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:27">
+    <row r="26" customFormat="1" spans="1:26">
       <c r="A26" s="4" t="s">
         <v>48</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>419.69</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:27">
+    <row r="27" customFormat="1" spans="1:26">
       <c r="A27" s="4" t="s">
         <v>49</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>455.22</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:27">
+    <row r="28" customFormat="1" spans="1:26">
       <c r="A28" s="4" t="s">
         <v>50</v>
       </c>
@@ -3352,79 +3352,79 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>560.7</v>
+        <v>539.82</v>
       </c>
       <c r="D28" s="4">
-        <v>510.85</v>
+        <v>491.89</v>
       </c>
       <c r="E28" s="4">
-        <v>472.06</v>
+        <v>471.41</v>
       </c>
       <c r="F28" s="4">
-        <v>441.16</v>
+        <v>439.84</v>
       </c>
       <c r="G28" s="4">
-        <v>406.3</v>
+        <v>406.07</v>
       </c>
       <c r="H28" s="4">
-        <v>398.1</v>
+        <v>399.45</v>
       </c>
       <c r="I28" s="4">
-        <v>414.43</v>
+        <v>411.77</v>
       </c>
       <c r="J28" s="4">
-        <v>404.81</v>
+        <v>401.8</v>
       </c>
       <c r="K28" s="4">
-        <v>473.86</v>
+        <v>463.42</v>
       </c>
       <c r="L28" s="4">
-        <v>512.45</v>
+        <v>504.2</v>
       </c>
       <c r="M28" s="4">
-        <v>496.73</v>
+        <v>494.03</v>
       </c>
       <c r="N28" s="4">
-        <v>571.3</v>
+        <v>542.86</v>
       </c>
       <c r="O28" s="4">
-        <v>554.9</v>
+        <v>537.46</v>
       </c>
       <c r="P28" s="4">
-        <v>596.05</v>
+        <v>570.74</v>
       </c>
       <c r="Q28" s="4">
-        <v>511.08</v>
+        <v>525.63</v>
       </c>
       <c r="R28" s="4">
-        <v>556.64</v>
+        <v>530.29</v>
       </c>
       <c r="S28" s="4">
-        <v>602.19</v>
+        <v>599.48</v>
       </c>
       <c r="T28" s="4">
-        <v>632.07</v>
+        <v>623.26</v>
       </c>
       <c r="U28" s="4">
-        <v>698.55</v>
+        <v>652.77</v>
       </c>
       <c r="V28" s="4">
-        <v>757.2</v>
+        <v>716.98</v>
       </c>
       <c r="W28" s="4">
-        <v>747.78</v>
+        <v>707.84</v>
       </c>
       <c r="X28" s="4">
-        <v>666.66</v>
+        <v>655.92</v>
       </c>
       <c r="Y28" s="4">
-        <v>644.72</v>
+        <v>634.1</v>
       </c>
       <c r="Z28" s="4">
-        <v>500.39</v>
+        <v>480.07</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:27">
+    <row r="29" customFormat="1" spans="1:26">
       <c r="A29" s="4" t="s">
         <v>51</v>
       </c>
@@ -3502,9 +3502,6 @@
       </c>
       <c r="Z29" s="4">
         <v>491.06</v>
-      </c>
-      <c r="AA29">
-        <v>537.66</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -3352,76 +3352,76 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>539.82</v>
+        <v>540.39</v>
       </c>
       <c r="D28" s="4">
-        <v>491.89</v>
+        <v>492.51</v>
       </c>
       <c r="E28" s="4">
-        <v>471.41</v>
+        <v>473.1</v>
       </c>
       <c r="F28" s="4">
-        <v>439.84</v>
+        <v>440.98</v>
       </c>
       <c r="G28" s="4">
-        <v>406.07</v>
+        <v>406.9</v>
       </c>
       <c r="H28" s="4">
-        <v>399.45</v>
+        <v>399.93</v>
       </c>
       <c r="I28" s="4">
-        <v>411.77</v>
+        <v>412.14</v>
       </c>
       <c r="J28" s="4">
-        <v>401.8</v>
+        <v>403.15</v>
       </c>
       <c r="K28" s="4">
-        <v>463.42</v>
+        <v>445.14</v>
       </c>
       <c r="L28" s="4">
-        <v>504.2</v>
+        <v>483.97</v>
       </c>
       <c r="M28" s="4">
-        <v>494.03</v>
+        <v>474.74</v>
       </c>
       <c r="N28" s="4">
-        <v>542.86</v>
+        <v>519.84</v>
       </c>
       <c r="O28" s="4">
-        <v>537.46</v>
+        <v>515.19</v>
       </c>
       <c r="P28" s="4">
-        <v>570.74</v>
+        <v>549.46</v>
       </c>
       <c r="Q28" s="4">
-        <v>525.63</v>
+        <v>505.4</v>
       </c>
       <c r="R28" s="4">
-        <v>530.29</v>
+        <v>513.07</v>
       </c>
       <c r="S28" s="4">
-        <v>599.48</v>
+        <v>598.6</v>
       </c>
       <c r="T28" s="4">
-        <v>623.26</v>
+        <v>620.69</v>
       </c>
       <c r="U28" s="4">
-        <v>652.77</v>
+        <v>572.77</v>
       </c>
       <c r="V28" s="4">
-        <v>716.98</v>
+        <v>630.37</v>
       </c>
       <c r="W28" s="4">
-        <v>707.84</v>
+        <v>623.5</v>
       </c>
       <c r="X28" s="4">
-        <v>655.92</v>
+        <v>654.29</v>
       </c>
       <c r="Y28" s="4">
-        <v>634.1</v>
+        <v>634.6</v>
       </c>
       <c r="Z28" s="4">
-        <v>480.07</v>
+        <v>480.48</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:26">
@@ -3432,76 +3432,76 @@
         <v>27</v>
       </c>
       <c r="C29" s="4">
-        <v>549.36</v>
+        <v>540.27</v>
       </c>
       <c r="D29" s="4">
-        <v>500.27</v>
+        <v>481.33</v>
       </c>
       <c r="E29" s="4">
-        <v>461.6</v>
+        <v>467.16</v>
       </c>
       <c r="F29" s="4">
-        <v>433.94</v>
+        <v>453.92</v>
       </c>
       <c r="G29" s="4">
-        <v>402.61</v>
+        <v>433.24</v>
       </c>
       <c r="H29" s="4">
-        <v>393.8</v>
+        <v>432.27</v>
       </c>
       <c r="I29" s="4">
-        <v>409.62</v>
+        <v>421.9</v>
       </c>
       <c r="J29" s="4">
-        <v>398.75</v>
+        <v>429.7</v>
       </c>
       <c r="K29" s="4">
-        <v>464.53</v>
+        <v>470.89</v>
       </c>
       <c r="L29" s="4">
-        <v>504.77</v>
+        <v>492.28</v>
       </c>
       <c r="M29" s="4">
-        <v>492.01</v>
+        <v>478.47</v>
       </c>
       <c r="N29" s="4">
-        <v>562.74</v>
+        <v>525.35</v>
       </c>
       <c r="O29" s="4">
-        <v>553.45</v>
+        <v>503.98</v>
       </c>
       <c r="P29" s="4">
-        <v>586.52</v>
+        <v>550.92</v>
       </c>
       <c r="Q29" s="4">
-        <v>508.23</v>
+        <v>524.92</v>
       </c>
       <c r="R29" s="4">
-        <v>550.73</v>
+        <v>543</v>
       </c>
       <c r="S29" s="4">
-        <v>583.9</v>
+        <v>599.61</v>
       </c>
       <c r="T29" s="4">
-        <v>611.85</v>
+        <v>648.5</v>
       </c>
       <c r="U29" s="4">
-        <v>680.19</v>
+        <v>683.31</v>
       </c>
       <c r="V29" s="4">
-        <v>739.27</v>
+        <v>751.12</v>
       </c>
       <c r="W29" s="4">
-        <v>734.86</v>
+        <v>753.76</v>
       </c>
       <c r="X29" s="4">
-        <v>654.85</v>
+        <v>716.77</v>
       </c>
       <c r="Y29" s="4">
-        <v>634.91</v>
+        <v>652.09</v>
       </c>
       <c r="Z29" s="4">
-        <v>491.06</v>
+        <v>514.18</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="13580"/>
+    <workbookView windowWidth="22960" windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>日期</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3352,76 +3355,76 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>540.39</v>
+        <v>604.6</v>
       </c>
       <c r="D28" s="4">
-        <v>492.51</v>
+        <v>494.1</v>
       </c>
       <c r="E28" s="4">
-        <v>473.1</v>
+        <v>461.7</v>
       </c>
       <c r="F28" s="4">
-        <v>440.98</v>
+        <v>434.6</v>
       </c>
       <c r="G28" s="4">
-        <v>406.9</v>
+        <v>412.6</v>
       </c>
       <c r="H28" s="4">
-        <v>399.93</v>
+        <v>423.4</v>
       </c>
       <c r="I28" s="4">
-        <v>412.14</v>
+        <v>408.6</v>
       </c>
       <c r="J28" s="4">
-        <v>403.15</v>
+        <v>401.7</v>
       </c>
       <c r="K28" s="4">
-        <v>445.14</v>
+        <v>435.8</v>
       </c>
       <c r="L28" s="4">
-        <v>483.97</v>
+        <v>459.1</v>
       </c>
       <c r="M28" s="4">
-        <v>474.74</v>
+        <v>447.1</v>
       </c>
       <c r="N28" s="4">
-        <v>519.84</v>
+        <v>466.5</v>
       </c>
       <c r="O28" s="4">
-        <v>515.19</v>
+        <v>453.5</v>
       </c>
       <c r="P28" s="4">
-        <v>549.46</v>
+        <v>501.8</v>
       </c>
       <c r="Q28" s="4">
-        <v>505.4</v>
+        <v>514.6</v>
       </c>
       <c r="R28" s="4">
-        <v>513.07</v>
+        <v>524.9</v>
       </c>
       <c r="S28" s="4">
-        <v>598.6</v>
+        <v>588.1</v>
       </c>
       <c r="T28" s="4">
-        <v>620.69</v>
+        <v>548.2</v>
       </c>
       <c r="U28" s="4">
-        <v>572.77</v>
+        <v>520.8</v>
       </c>
       <c r="V28" s="4">
-        <v>630.37</v>
+        <v>615.5</v>
       </c>
       <c r="W28" s="4">
-        <v>623.5</v>
+        <v>623.6</v>
       </c>
       <c r="X28" s="4">
-        <v>654.29</v>
+        <v>628.6</v>
       </c>
       <c r="Y28" s="4">
-        <v>634.6</v>
+        <v>635.6</v>
       </c>
       <c r="Z28" s="4">
-        <v>480.48</v>
+        <v>472</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:26">
@@ -3432,76 +3435,156 @@
         <v>27</v>
       </c>
       <c r="C29" s="4">
-        <v>540.27</v>
+        <v>605.2</v>
       </c>
       <c r="D29" s="4">
-        <v>481.33</v>
+        <v>501.9</v>
       </c>
       <c r="E29" s="4">
-        <v>467.16</v>
+        <v>463.6</v>
       </c>
       <c r="F29" s="4">
-        <v>453.92</v>
+        <v>434.8</v>
       </c>
       <c r="G29" s="4">
-        <v>433.24</v>
+        <v>420.6</v>
       </c>
       <c r="H29" s="4">
-        <v>432.27</v>
+        <v>431.1</v>
       </c>
       <c r="I29" s="4">
-        <v>421.9</v>
+        <v>420</v>
       </c>
       <c r="J29" s="4">
-        <v>429.7</v>
+        <v>412.6</v>
       </c>
       <c r="K29" s="4">
-        <v>470.89</v>
+        <v>441.8</v>
       </c>
       <c r="L29" s="4">
-        <v>492.28</v>
+        <v>476.9</v>
       </c>
       <c r="M29" s="4">
-        <v>478.47</v>
+        <v>463.4</v>
       </c>
       <c r="N29" s="4">
-        <v>525.35</v>
+        <v>485.5</v>
       </c>
       <c r="O29" s="4">
-        <v>503.98</v>
+        <v>475.3</v>
       </c>
       <c r="P29" s="4">
-        <v>550.92</v>
+        <v>528.2</v>
       </c>
       <c r="Q29" s="4">
-        <v>524.92</v>
+        <v>530</v>
       </c>
       <c r="R29" s="4">
-        <v>543</v>
+        <v>528.3</v>
       </c>
       <c r="S29" s="4">
-        <v>599.61</v>
+        <v>598</v>
       </c>
       <c r="T29" s="4">
-        <v>648.5</v>
+        <v>545.9</v>
       </c>
       <c r="U29" s="4">
-        <v>683.31</v>
+        <v>569.6</v>
       </c>
       <c r="V29" s="4">
-        <v>751.12</v>
+        <v>692.9</v>
       </c>
       <c r="W29" s="4">
-        <v>753.76</v>
+        <v>707.4</v>
       </c>
       <c r="X29" s="4">
-        <v>716.77</v>
+        <v>662.2</v>
       </c>
       <c r="Y29" s="4">
-        <v>652.09</v>
+        <v>660.5</v>
       </c>
       <c r="Z29" s="4">
-        <v>514.18</v>
+        <v>496.9</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:26">
+      <c r="A30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="4">
+        <v>603.21</v>
+      </c>
+      <c r="D30" s="4">
+        <v>540.12</v>
+      </c>
+      <c r="E30" s="4">
+        <v>531.52</v>
+      </c>
+      <c r="F30" s="4">
+        <v>495.94</v>
+      </c>
+      <c r="G30" s="4">
+        <v>461.67</v>
+      </c>
+      <c r="H30" s="4">
+        <v>475.93</v>
+      </c>
+      <c r="I30" s="4">
+        <v>454.35</v>
+      </c>
+      <c r="J30" s="4">
+        <v>460.69</v>
+      </c>
+      <c r="K30" s="4">
+        <v>533.68</v>
+      </c>
+      <c r="L30" s="4">
+        <v>575.89</v>
+      </c>
+      <c r="M30" s="4">
+        <v>563.43</v>
+      </c>
+      <c r="N30" s="4">
+        <v>609.34</v>
+      </c>
+      <c r="O30" s="4">
+        <v>573.24</v>
+      </c>
+      <c r="P30" s="4">
+        <v>625.7</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>636.86</v>
+      </c>
+      <c r="R30" s="4">
+        <v>622.93</v>
+      </c>
+      <c r="S30" s="4">
+        <v>670.13</v>
+      </c>
+      <c r="T30" s="4">
+        <v>678.98</v>
+      </c>
+      <c r="U30" s="4">
+        <v>642.14</v>
+      </c>
+      <c r="V30" s="4">
+        <v>726.63</v>
+      </c>
+      <c r="W30" s="4">
+        <v>716.63</v>
+      </c>
+      <c r="X30" s="4">
+        <v>725.11</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>681.02</v>
+      </c>
+      <c r="Z30" s="4">
+        <v>539.31</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22960" windowHeight="13580"/>
+    <workbookView windowWidth="31140" windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -3489,13 +3489,13 @@
         <v>545.9</v>
       </c>
       <c r="U29" s="4">
-        <v>569.6</v>
+        <v>527.4</v>
       </c>
       <c r="V29" s="4">
-        <v>692.9</v>
+        <v>641.6</v>
       </c>
       <c r="W29" s="4">
-        <v>707.4</v>
+        <v>655</v>
       </c>
       <c r="X29" s="4">
         <v>662.2</v>
@@ -3515,76 +3515,76 @@
         <v>27</v>
       </c>
       <c r="C30" s="4">
-        <v>603.21</v>
+        <v>548.7</v>
       </c>
       <c r="D30" s="4">
-        <v>540.12</v>
+        <v>493.8</v>
       </c>
       <c r="E30" s="4">
-        <v>531.52</v>
+        <v>468.8</v>
       </c>
       <c r="F30" s="4">
-        <v>495.94</v>
+        <v>447.7</v>
       </c>
       <c r="G30" s="4">
-        <v>461.67</v>
+        <v>429.1</v>
       </c>
       <c r="H30" s="4">
-        <v>475.93</v>
+        <v>442</v>
       </c>
       <c r="I30" s="4">
-        <v>454.35</v>
+        <v>423.5</v>
       </c>
       <c r="J30" s="4">
-        <v>460.69</v>
+        <v>412.7</v>
       </c>
       <c r="K30" s="4">
-        <v>533.68</v>
+        <v>470.6</v>
       </c>
       <c r="L30" s="4">
-        <v>575.89</v>
+        <v>507.9</v>
       </c>
       <c r="M30" s="4">
-        <v>563.43</v>
+        <v>504.1</v>
       </c>
       <c r="N30" s="4">
-        <v>609.34</v>
+        <v>524.1</v>
       </c>
       <c r="O30" s="4">
-        <v>573.24</v>
+        <v>516.6</v>
       </c>
       <c r="P30" s="4">
-        <v>625.7</v>
+        <v>584.5</v>
       </c>
       <c r="Q30" s="4">
-        <v>636.86</v>
+        <v>548.4</v>
       </c>
       <c r="R30" s="4">
-        <v>622.93</v>
+        <v>559.2</v>
       </c>
       <c r="S30" s="4">
-        <v>670.13</v>
+        <v>572.9</v>
       </c>
       <c r="T30" s="4">
-        <v>678.98</v>
+        <v>561.2</v>
       </c>
       <c r="U30" s="4">
-        <v>642.14</v>
+        <v>584.3</v>
       </c>
       <c r="V30" s="4">
-        <v>726.63</v>
+        <v>666.3</v>
       </c>
       <c r="W30" s="4">
-        <v>716.63</v>
+        <v>632.9</v>
       </c>
       <c r="X30" s="4">
-        <v>725.11</v>
+        <v>667.7</v>
       </c>
       <c r="Y30" s="4">
-        <v>681.02</v>
+        <v>610.8</v>
       </c>
       <c r="Z30" s="4">
-        <v>539.31</v>
+        <v>489.4</v>
       </c>
     </row>
   </sheetData>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
   <si>
     <t>日期</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3587,6 +3590,86 @@
         <v>489.4</v>
       </c>
     </row>
+    <row r="31" customFormat="1" spans="1:26">
+      <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="4">
+        <v>571.46</v>
+      </c>
+      <c r="D31" s="4">
+        <v>498.71</v>
+      </c>
+      <c r="E31" s="4">
+        <v>458.54</v>
+      </c>
+      <c r="F31" s="4">
+        <v>418.14</v>
+      </c>
+      <c r="G31" s="4">
+        <v>414.23</v>
+      </c>
+      <c r="H31" s="4">
+        <v>414.26</v>
+      </c>
+      <c r="I31" s="4">
+        <v>389.06</v>
+      </c>
+      <c r="J31" s="4">
+        <v>373.14</v>
+      </c>
+      <c r="K31" s="4">
+        <v>435.97</v>
+      </c>
+      <c r="L31" s="4">
+        <v>499.43</v>
+      </c>
+      <c r="M31" s="4">
+        <v>475.29</v>
+      </c>
+      <c r="N31" s="4">
+        <v>500.62</v>
+      </c>
+      <c r="O31" s="4">
+        <v>485.62</v>
+      </c>
+      <c r="P31" s="4">
+        <v>566.42</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>523.06</v>
+      </c>
+      <c r="R31" s="4">
+        <v>525.12</v>
+      </c>
+      <c r="S31" s="4">
+        <v>563.38</v>
+      </c>
+      <c r="T31" s="4">
+        <v>532.73</v>
+      </c>
+      <c r="U31" s="4">
+        <v>523.53</v>
+      </c>
+      <c r="V31" s="4">
+        <v>599.44</v>
+      </c>
+      <c r="W31" s="4">
+        <v>591.3</v>
+      </c>
+      <c r="X31" s="4">
+        <v>583.5</v>
+      </c>
+      <c r="Y31" s="4">
+        <v>565.81</v>
+      </c>
+      <c r="Z31" s="4">
+        <v>432.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31140" windowHeight="13580"/>
+    <workbookView windowWidth="29920" windowHeight="13580"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>日期</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1182,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3670,6 +3673,86 @@
         <v>432.7</v>
       </c>
     </row>
+    <row r="32" customFormat="1" spans="1:26">
+      <c r="A32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="4">
+        <v>512.16</v>
+      </c>
+      <c r="D32" s="4">
+        <v>483.87</v>
+      </c>
+      <c r="E32" s="4">
+        <v>436.83</v>
+      </c>
+      <c r="F32" s="4">
+        <v>416.49</v>
+      </c>
+      <c r="G32" s="4">
+        <v>406.86</v>
+      </c>
+      <c r="H32" s="4">
+        <v>396.42</v>
+      </c>
+      <c r="I32" s="4">
+        <v>380.41</v>
+      </c>
+      <c r="J32" s="4">
+        <v>378.49</v>
+      </c>
+      <c r="K32" s="4">
+        <v>424.4</v>
+      </c>
+      <c r="L32" s="4">
+        <v>471.25</v>
+      </c>
+      <c r="M32" s="4">
+        <v>453.29</v>
+      </c>
+      <c r="N32" s="4">
+        <v>477.3</v>
+      </c>
+      <c r="O32" s="4">
+        <v>430.68</v>
+      </c>
+      <c r="P32" s="4">
+        <v>515.95</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>492.28</v>
+      </c>
+      <c r="R32" s="4">
+        <v>491.97</v>
+      </c>
+      <c r="S32" s="4">
+        <v>521.9</v>
+      </c>
+      <c r="T32" s="4">
+        <v>519.1</v>
+      </c>
+      <c r="U32" s="4">
+        <v>488.03</v>
+      </c>
+      <c r="V32" s="4">
+        <v>561.72</v>
+      </c>
+      <c r="W32" s="4">
+        <v>525.36</v>
+      </c>
+      <c r="X32" s="4">
+        <v>491.29</v>
+      </c>
+      <c r="Y32" s="4">
+        <v>486.86</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>413.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>日期</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3753,6 +3756,86 @@
         <v>413.66</v>
       </c>
     </row>
+    <row r="33" customFormat="1" spans="1:26">
+      <c r="A33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4">
+        <v>486.02</v>
+      </c>
+      <c r="D33" s="4">
+        <v>438.78</v>
+      </c>
+      <c r="E33" s="4">
+        <v>407.7</v>
+      </c>
+      <c r="F33" s="4">
+        <v>393.98</v>
+      </c>
+      <c r="G33" s="4">
+        <v>385.23</v>
+      </c>
+      <c r="H33" s="4">
+        <v>381.3</v>
+      </c>
+      <c r="I33" s="4">
+        <v>368.72</v>
+      </c>
+      <c r="J33" s="4">
+        <v>344.23</v>
+      </c>
+      <c r="K33" s="4">
+        <v>360.11</v>
+      </c>
+      <c r="L33" s="4">
+        <v>379.62</v>
+      </c>
+      <c r="M33" s="4">
+        <v>378.06</v>
+      </c>
+      <c r="N33" s="4">
+        <v>414.17</v>
+      </c>
+      <c r="O33" s="4">
+        <v>391.64</v>
+      </c>
+      <c r="P33" s="4">
+        <v>448.33</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>432.3</v>
+      </c>
+      <c r="R33" s="4">
+        <v>427.57</v>
+      </c>
+      <c r="S33" s="4">
+        <v>478.89</v>
+      </c>
+      <c r="T33" s="4">
+        <v>476.89</v>
+      </c>
+      <c r="U33" s="4">
+        <v>452.66</v>
+      </c>
+      <c r="V33" s="4">
+        <v>497.52</v>
+      </c>
+      <c r="W33" s="4">
+        <v>480.09</v>
+      </c>
+      <c r="X33" s="4">
+        <v>466.21</v>
+      </c>
+      <c r="Y33" s="4">
+        <v>444.93</v>
+      </c>
+      <c r="Z33" s="4">
+        <v>392.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
   <si>
     <t>日期</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3836,6 +3839,86 @@
         <v>392.27</v>
       </c>
     </row>
+    <row r="34" customFormat="1" spans="1:26">
+      <c r="A34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="4">
+        <v>435.61</v>
+      </c>
+      <c r="D34" s="4">
+        <v>416.39</v>
+      </c>
+      <c r="E34" s="4">
+        <v>374.31</v>
+      </c>
+      <c r="F34" s="4">
+        <v>364.09</v>
+      </c>
+      <c r="G34" s="4">
+        <v>346.7</v>
+      </c>
+      <c r="H34" s="4">
+        <v>347.02</v>
+      </c>
+      <c r="I34" s="4">
+        <v>341.07</v>
+      </c>
+      <c r="J34" s="4">
+        <v>335.35</v>
+      </c>
+      <c r="K34" s="4">
+        <v>402.48</v>
+      </c>
+      <c r="L34" s="4">
+        <v>441.83</v>
+      </c>
+      <c r="M34" s="4">
+        <v>421.91</v>
+      </c>
+      <c r="N34" s="4">
+        <v>451.78</v>
+      </c>
+      <c r="O34" s="4">
+        <v>417.64</v>
+      </c>
+      <c r="P34" s="4">
+        <v>480.4</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>441.02</v>
+      </c>
+      <c r="R34" s="4">
+        <v>455.96</v>
+      </c>
+      <c r="S34" s="4">
+        <v>529.39</v>
+      </c>
+      <c r="T34" s="4">
+        <v>537.78</v>
+      </c>
+      <c r="U34" s="4">
+        <v>480.24</v>
+      </c>
+      <c r="V34" s="4">
+        <v>556.81</v>
+      </c>
+      <c r="W34" s="4">
+        <v>528.06</v>
+      </c>
+      <c r="X34" s="4">
+        <v>493.97</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>450.44</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>384.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/广东日前电价预测.xlsx
+++ b/广东日前电价预测.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29920" windowHeight="13580"/>
+    <workbookView windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="电价预测" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
   <si>
     <t>日期</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3919,6 +3922,86 @@
         <v>384.23</v>
       </c>
     </row>
+    <row r="35" customFormat="1" spans="1:26">
+      <c r="A35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="4">
+        <v>418.29</v>
+      </c>
+      <c r="D35" s="4">
+        <v>372.35</v>
+      </c>
+      <c r="E35" s="4">
+        <v>325.06</v>
+      </c>
+      <c r="F35" s="4">
+        <v>307.45</v>
+      </c>
+      <c r="G35" s="4">
+        <v>291.71</v>
+      </c>
+      <c r="H35" s="4">
+        <v>293.71</v>
+      </c>
+      <c r="I35" s="4">
+        <v>290.19</v>
+      </c>
+      <c r="J35" s="4">
+        <v>280.84</v>
+      </c>
+      <c r="K35" s="4">
+        <v>313.62</v>
+      </c>
+      <c r="L35" s="4">
+        <v>335.96</v>
+      </c>
+      <c r="M35" s="4">
+        <v>330.18</v>
+      </c>
+      <c r="N35" s="4">
+        <v>351.71</v>
+      </c>
+      <c r="O35" s="4">
+        <v>357.45</v>
+      </c>
+      <c r="P35" s="4">
+        <v>388.09</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>371.3</v>
+      </c>
+      <c r="R35" s="4">
+        <v>400.2</v>
+      </c>
+      <c r="S35" s="4">
+        <v>443.63</v>
+      </c>
+      <c r="T35" s="4">
+        <v>471.02</v>
+      </c>
+      <c r="U35" s="4">
+        <v>440.95</v>
+      </c>
+      <c r="V35" s="4">
+        <v>487.42</v>
+      </c>
+      <c r="W35" s="4">
+        <v>466.7</v>
+      </c>
+      <c r="X35" s="4">
+        <v>458.44</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>426.47</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>363.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
